--- a/output/year1_summary_2026-10-29.xlsx
+++ b/output/year1_summary_2026-10-29.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="497" uniqueCount="497">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="501" uniqueCount="501">
   <si>
     <t xml:space="preserve">State</t>
   </si>
@@ -219,6 +219,9 @@
     <t xml:space="preserve">4 Complete of 50</t>
   </si>
   <si>
+    <t xml:space="preserve">States with ≥50% published (n = 22)</t>
+  </si>
+  <si>
     <t xml:space="preserve">n/m</t>
   </si>
   <si>
@@ -510,6 +513,12 @@
     <t xml:space="preserve">4 COMPLETE of 50</t>
   </si>
   <si>
+    <t xml:space="preserve">US_GE50</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4 COMPLETE of 22: AK AL AR CA CO FL GA ID IN MD MI MS NJ NV OH OR RI SC SD TX VT WY</t>
+  </si>
+  <si>
     <t xml:space="preserve">sheet</t>
   </si>
   <si>
@@ -522,7 +531,7 @@
     <t xml:space="preserve">Overview</t>
   </si>
   <si>
-    <t xml:space="preserve">State name; the last row is the national total (the sum of the 50 state rows).</t>
+    <t xml:space="preserve">State name. Below the 50 states: the national total (the sum of the 50 state rows), then the states whose awards published are at least 50% of their allotment (n in the label), which shows only allotment, awards published, the hospital figures and strict named-hospital dollars. The second row is a subset of the national total, never added to it.</t>
   </si>
   <si>
     <t xml:space="preserve">Plain-language Year 1 status; each label is defined below.</t>
@@ -573,7 +582,7 @@
     <t xml:space="preserve">Detail</t>
   </si>
   <si>
-    <t xml:space="preserve">Two-letter state code; US is the national row (the sum of the 50 state rows).</t>
+    <t xml:space="preserve">Two-letter state code. US is the national row (the sum of the 50 state rows). US_GE50 is the second national row: the sum over the states whose awards published are at least 50% of their allotment (a subset of US, never added to it).</t>
   </si>
   <si>
     <t xml:space="preserve">State name.</t>
@@ -687,7 +696,7 @@
     <t xml:space="preserve">note</t>
   </si>
   <si>
-    <t xml:space="preserve">HOW TO READ THIS. Start on Overview (one row per state, national total last): 'Hospital $ (best estimate)' is the headline figure, 'Strict named-hospital $' the source-confirmed floor; Detail carries every column, Definitions defines each column and status label, Sources lists the documents.</t>
+    <t xml:space="preserve">HOW TO READ THIS. Start on Overview (one row per state, then the national total and the states with at least half their money published): 'Hospital $ (best estimate)' is the headline figure, 'Strict named-hospital $' the source-confirmed floor; Detail carries every column, Definitions defines each column and status label, Sources lists the documents.</t>
   </si>
   <si>
     <t xml:space="preserve">DATA AS OF 2026-10-29. Built by R/08_year1_summary.R from the committed award files; every figure traces to an archived state or CMS source (Sources sheet).</t>
@@ -723,7 +732,10 @@
     <t xml:space="preserve">AWARD COVERAGE VARIES WIDELY BY STATE. Awards published run from 0% to 97.6% of the allotment, so a state's hospital share describes only the money that state has published so far. State shares are not comparable to one another.</t>
   </si>
   <si>
-    <t xml:space="preserve">n/m (HOSPITAL % OF AWARDS). Shown only where awards published are at least 50% of the allotment. Not meaningful where most of the state's money is not yet published; e.g., Illinois's only published award is ICAHN's hospital network grant. Hospital % of allotment is shown for every state.</t>
+    <t xml:space="preserve">n/m (HOSPITAL % OF AWARDS). Shown only where awards published are at least 50% of the allotment. Not meaningful where most of the state's money is not yet published; e.g., Illinois's only published award is ICAHN's hospital network grant. The national hospital share of awards is reported only for states where most of the money is published (see the second national row). Hospital % of allotment is shown for every state.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SECOND NATIONAL ROW. 'States with ≥50% published (n = 22)' sums the states whose awards published are at least 50% of their allotment (AK AL AR CA CO FL GA ID IN MD MI MS NJ NV OH OR RI SC SD TX VT WY): allotment $4,440,562,268, awards published $3,441,569,061, hospital best estimate $1,572,986,177 (45.7% of those awards). It is a subset of the national row, never added to it. Rhode Island qualifies on CMS obligation-report lines alone; the set changes as states publish.</t>
   </si>
   <si>
     <t xml:space="preserve">CONFIDENTIAL SOURCES. Figures or rows flagged here rest on, or cite, Delaware's confidential source (DE Verify.xlsx). They must not leave the team. As built, no award row or figure cites it; Delaware's status-table notes do (confidential_source_flag; the row is shaded on Overview and Detail).</t>
@@ -1577,19 +1589,19 @@
     <xf numFmtId="167" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
+    <xf numFmtId="166" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyNumberFormat="1"/>
+    <xf numFmtId="167" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyNumberFormat="1"/>
+    <xf numFmtId="167" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="166" fontId="2" fillId="3" borderId="0" xfId="0" applyFont="1" applyNumberFormat="1" applyFill="1"/>
     <xf numFmtId="167" fontId="2" fillId="3" borderId="0" xfId="0" applyFont="1" applyNumberFormat="1" applyFill="1"/>
     <xf numFmtId="167" fontId="2" fillId="3" borderId="0" xfId="0" applyFont="1" applyNumberFormat="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="166" fontId="1" fillId="3" borderId="0" xfId="0" applyFont="1" applyNumberFormat="1" applyFill="1"/>
-    <xf numFmtId="167" fontId="1" fillId="3" borderId="0" xfId="0" applyFont="1" applyNumberFormat="1" applyFill="1"/>
-    <xf numFmtId="167" fontId="1" fillId="3" borderId="0" xfId="0" applyFont="1" applyNumberFormat="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
@@ -1888,7 +1900,7 @@
   <dimension ref="A1"/>
   <sheetFormatPr defaultRowHeight="15.0" baseColWidth="10"/>
   <cols>
-    <col min="1" max="1" width="23.71" hidden="0" customWidth="1"/>
+    <col min="1" max="1" width="38.71" hidden="0" customWidth="1"/>
     <col min="2" max="2" width="31.71" hidden="0" customWidth="1"/>
     <col min="3" max="3" width="19.71" hidden="0" customWidth="1"/>
     <col min="4" max="4" width="19.71" hidden="0" customWidth="1"/>
@@ -2016,7 +2028,7 @@
         <v>0</v>
       </c>
       <c r="G4" s="4" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="H4" s="3" t="n">
         <v>0</v>
@@ -2144,7 +2156,7 @@
         <v>46000000</v>
       </c>
       <c r="G8" s="4" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="H8" s="3" t="n">
         <v>0.298218908315747</v>
@@ -2163,25 +2175,25 @@
       <c r="B9" s="12" t="s">
         <v>13</v>
       </c>
-      <c r="C9" s="5" t="n">
+      <c r="C9" s="9" t="n">
         <v>157394964</v>
       </c>
-      <c r="D9" s="5" t="n">
+      <c r="D9" s="9" t="n">
         <v>22690000</v>
       </c>
-      <c r="E9" s="6" t="n">
+      <c r="E9" s="10" t="n">
         <v>0.144159631435222</v>
       </c>
-      <c r="F9" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="G9" s="7" t="s">
-        <v>67</v>
-      </c>
-      <c r="H9" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="I9" s="5" t="n">
+      <c r="F9" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="G9" s="11" t="s">
+        <v>68</v>
+      </c>
+      <c r="H9" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="I9" s="9" t="n">
         <v>0</v>
       </c>
       <c r="J9" s="12" t="n">
@@ -2272,7 +2284,7 @@
         <v>0</v>
       </c>
       <c r="G12" s="4" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="H12" s="3" t="n">
         <v>0</v>
@@ -2336,7 +2348,7 @@
         <v>50008264</v>
       </c>
       <c r="G14" s="4" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="H14" s="3" t="n">
         <v>0.258549918586779</v>
@@ -2400,7 +2412,7 @@
         <v>0</v>
       </c>
       <c r="G16" s="4" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="H16" s="3" t="n">
         <v>0</v>
@@ -2432,7 +2444,7 @@
         <v>62562949</v>
       </c>
       <c r="G17" s="4" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="H17" s="3" t="n">
         <v>0.281944617546995</v>
@@ -2464,7 +2476,7 @@
         <v>0</v>
       </c>
       <c r="G18" s="4" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="H18" s="3" t="n">
         <v>0</v>
@@ -2496,7 +2508,7 @@
         <v>1500000</v>
       </c>
       <c r="G19" s="4" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="H19" s="3" t="n">
         <v>0.00719857935748437</v>
@@ -2528,7 +2540,7 @@
         <v>0</v>
       </c>
       <c r="G20" s="4" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="H20" s="3" t="n">
         <v>0</v>
@@ -2592,7 +2604,7 @@
         <v>0</v>
       </c>
       <c r="G22" s="4" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="H22" s="3" t="n">
         <v>0</v>
@@ -2656,7 +2668,7 @@
         <v>0</v>
       </c>
       <c r="G24" s="4" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="H24" s="3" t="n">
         <v>0</v>
@@ -2720,7 +2732,7 @@
         <v>34646479.34</v>
       </c>
       <c r="G26" s="4" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="H26" s="3" t="n">
         <v>0.1601950669535</v>
@@ -2752,7 +2764,7 @@
         <v>0</v>
       </c>
       <c r="G27" s="4" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="H27" s="3" t="n">
         <v>0</v>
@@ -2784,7 +2796,7 @@
         <v>36619908.12</v>
       </c>
       <c r="G28" s="4" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="H28" s="3" t="n">
         <v>0.167574534967487</v>
@@ -2848,7 +2860,7 @@
         <v>17500000</v>
       </c>
       <c r="G30" s="4" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="H30" s="3" t="n">
         <v>0.0857773548273412</v>
@@ -2912,7 +2924,7 @@
         <v>0</v>
       </c>
       <c r="G32" s="4" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="H32" s="3" t="n">
         <v>0</v>
@@ -2944,7 +2956,7 @@
         <v>47358790.79</v>
       </c>
       <c r="G33" s="4" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="H33" s="3" t="n">
         <v>0.223329203979692</v>
@@ -2976,7 +2988,7 @@
         <v>0</v>
       </c>
       <c r="G34" s="4" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="H34" s="3" t="n">
         <v>0</v>
@@ -3008,7 +3020,7 @@
         <v>0</v>
       </c>
       <c r="G35" s="4" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="H35" s="3" t="n">
         <v>0</v>
@@ -3072,7 +3084,7 @@
         <v>33403159.16</v>
       </c>
       <c r="G37" s="4" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="H37" s="3" t="n">
         <v>0.149470266662715</v>
@@ -3136,7 +3148,7 @@
         <v>27112688</v>
       </c>
       <c r="G39" s="4" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="H39" s="3" t="n">
         <v>0.140266539186974</v>
@@ -3264,7 +3276,7 @@
         <v>0</v>
       </c>
       <c r="G43" s="4" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="H43" s="3" t="n">
         <v>0</v>
@@ -3328,7 +3340,7 @@
         <v>0</v>
       </c>
       <c r="G45" s="4" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="H45" s="3" t="n">
         <v>0</v>
@@ -3392,7 +3404,7 @@
         <v>12031000</v>
       </c>
       <c r="G47" s="4" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="H47" s="3" t="n">
         <v>0.0634730913977485</v>
@@ -3424,7 +3436,7 @@
         <v>57170000</v>
       </c>
       <c r="G48" s="4" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="H48" s="3" t="n">
         <v>0.315407612203003</v>
@@ -3456,7 +3468,7 @@
         <v>6324000</v>
       </c>
       <c r="G49" s="4" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="H49" s="3" t="n">
         <v>0.0317030462882673</v>
@@ -3488,7 +3500,7 @@
         <v>0</v>
       </c>
       <c r="G50" s="4" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="H50" s="3" t="n">
         <v>0</v>
@@ -3533,36 +3545,62 @@
       </c>
     </row>
     <row r="52">
-      <c r="A52" s="11" t="s">
+      <c r="A52" s="8" t="s">
         <v>65</v>
       </c>
-      <c r="B52" s="11" t="s">
+      <c r="B52" s="8" t="s">
         <v>66</v>
       </c>
-      <c r="C52" s="8" t="n">
+      <c r="C52" s="5" t="n">
         <v>10000000003</v>
       </c>
-      <c r="D52" s="8" t="n">
+      <c r="D52" s="5" t="n">
         <v>4171734402.31</v>
       </c>
-      <c r="E52" s="9" t="n">
+      <c r="E52" s="6" t="n">
         <v>0.417173440105848</v>
       </c>
-      <c r="F52" s="8" t="n">
+      <c r="F52" s="5" t="n">
         <v>2005223415.77</v>
       </c>
-      <c r="G52" s="10" t="s">
+      <c r="G52" s="7" t="s">
+        <v>68</v>
+      </c>
+      <c r="H52" s="6" t="n">
+        <v>0.200522341516843</v>
+      </c>
+      <c r="I52" s="5" t="n">
+        <v>1731421723.08</v>
+      </c>
+      <c r="J52" s="8" t="n">
+        <v>269</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="8" t="s">
         <v>67</v>
       </c>
-      <c r="H52" s="9" t="n">
-        <v>0.200522341516843</v>
-      </c>
-      <c r="I52" s="8" t="n">
-        <v>1731421723.08</v>
-      </c>
-      <c r="J52" s="11" t="n">
-        <v>269</v>
-      </c>
+      <c r="B53" s="8"/>
+      <c r="C53" s="5" t="n">
+        <v>4440562268</v>
+      </c>
+      <c r="D53" s="5" t="n">
+        <v>3441569061.22</v>
+      </c>
+      <c r="E53" s="6"/>
+      <c r="F53" s="5" t="n">
+        <v>1572986177.36</v>
+      </c>
+      <c r="G53" s="6" t="n">
+        <v>0.45705495062836</v>
+      </c>
+      <c r="H53" s="6" t="n">
+        <v>0.354231307304348</v>
+      </c>
+      <c r="I53" s="5" t="n">
+        <v>1451104633.38</v>
+      </c>
+      <c r="J53" s="8"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -3575,9 +3613,9 @@
   <dimension ref="A1"/>
   <sheetFormatPr defaultRowHeight="15.0" baseColWidth="10"/>
   <cols>
-    <col min="1" max="1" width="8.71" hidden="0" customWidth="1"/>
-    <col min="2" max="2" width="23.71" hidden="0" customWidth="1"/>
-    <col min="3" max="3" width="47.71" hidden="0" customWidth="1"/>
+    <col min="1" max="1" width="10.71" hidden="0" customWidth="1"/>
+    <col min="2" max="2" width="38.71" hidden="0" customWidth="1"/>
+    <col min="3" max="3" width="60.71" hidden="0" customWidth="1"/>
     <col min="4" max="4" width="18.71" hidden="0" customWidth="1"/>
     <col min="5" max="5" width="14.71" hidden="0" customWidth="1"/>
     <col min="6" max="6" width="13.71" hidden="0" customWidth="1"/>
@@ -3616,126 +3654,126 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="J1" s="1" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="K1" s="1" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="L1" s="1" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="M1" s="1" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="N1" s="1" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="O1" s="1" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="P1" s="1" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="Q1" s="1" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="R1" s="1" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="S1" s="1" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="T1" s="1" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="U1" s="1" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="V1" s="1" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="W1" s="1" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="X1" s="1" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="Y1" s="1" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="Z1" s="1" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="AA1" s="1" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="AB1" s="1" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="AC1" s="1" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="AD1" s="1" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="AE1" s="1" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="AF1" s="1" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="AG1" s="1" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="AH1" s="1" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="AI1" s="1" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="AJ1" s="1" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="AK1" s="1" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="B2" t="s">
         <v>12</v>
       </c>
-      <c r="C2" t="s">
-        <v>106</v>
+      <c r="C2" s="15" t="s">
+        <v>107</v>
       </c>
       <c r="D2" s="2" t="n">
         <v>272174856</v>
@@ -3837,18 +3875,18 @@
         <v>0</v>
       </c>
       <c r="AK2" s="15" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="B3" t="s">
         <v>10</v>
       </c>
-      <c r="C3" t="s">
-        <v>109</v>
+      <c r="C3" s="15" t="s">
+        <v>110</v>
       </c>
       <c r="D3" s="2" t="n">
         <v>203404327</v>
@@ -3950,18 +3988,18 @@
         <v>0</v>
       </c>
       <c r="AK3" s="15" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="B4" t="s">
         <v>16</v>
       </c>
-      <c r="C4" t="s">
-        <v>109</v>
+      <c r="C4" s="15" t="s">
+        <v>110</v>
       </c>
       <c r="D4" s="2" t="n">
         <v>208779396</v>
@@ -4063,18 +4101,18 @@
         <v>0</v>
       </c>
       <c r="AK4" s="15" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="B5" t="s">
         <v>14</v>
       </c>
-      <c r="C5" t="s">
-        <v>112</v>
+      <c r="C5" s="15" t="s">
+        <v>113</v>
       </c>
       <c r="D5" s="2" t="n">
         <v>166988956</v>
@@ -4128,7 +4166,7 @@
         <v>0</v>
       </c>
       <c r="U5" s="4" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="V5" s="3" t="n">
         <v>0</v>
@@ -4176,18 +4214,18 @@
         <v>0</v>
       </c>
       <c r="AK5" s="15" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="B6" t="s">
         <v>17</v>
       </c>
-      <c r="C6" t="s">
-        <v>106</v>
+      <c r="C6" s="15" t="s">
+        <v>107</v>
       </c>
       <c r="D6" s="2" t="n">
         <v>233639308</v>
@@ -4289,18 +4327,18 @@
         <v>0</v>
       </c>
       <c r="AK6" s="15" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="B7" t="s">
         <v>18</v>
       </c>
-      <c r="C7" t="s">
-        <v>106</v>
+      <c r="C7" s="15" t="s">
+        <v>107</v>
       </c>
       <c r="D7" s="2" t="n">
         <v>200105604</v>
@@ -4402,18 +4440,18 @@
         <v>0</v>
       </c>
       <c r="AK7" s="15" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="B8" t="s">
         <v>19</v>
       </c>
-      <c r="C8" t="s">
-        <v>106</v>
+      <c r="C8" s="15" t="s">
+        <v>107</v>
       </c>
       <c r="D8" s="2" t="n">
         <v>154249106</v>
@@ -4467,7 +4505,7 @@
         <v>46000000</v>
       </c>
       <c r="U8" s="4" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="V8" s="3" t="n">
         <v>0.298218908315747</v>
@@ -4515,20 +4553,20 @@
         <v>0</v>
       </c>
       <c r="AK8" s="15" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="12" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="B9" s="12" t="s">
         <v>20</v>
       </c>
-      <c r="C9" s="12" t="s">
-        <v>106</v>
-      </c>
-      <c r="D9" s="5" t="n">
+      <c r="C9" s="14" t="s">
+        <v>107</v>
+      </c>
+      <c r="D9" s="9" t="n">
         <v>157394964</v>
       </c>
       <c r="E9" s="12" t="n">
@@ -4540,82 +4578,82 @@
       <c r="G9" s="12" t="n">
         <v>3</v>
       </c>
-      <c r="H9" s="5" t="n">
+      <c r="H9" s="9" t="n">
         <v>22690000</v>
       </c>
-      <c r="I9" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="J9" s="5" t="n">
+      <c r="I9" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="J9" s="9" t="n">
         <v>22690000</v>
       </c>
-      <c r="K9" s="6" t="n">
+      <c r="K9" s="10" t="n">
         <v>0.144159631435222</v>
       </c>
-      <c r="L9" s="5" t="n">
+      <c r="L9" s="9" t="n">
         <v>0</v>
       </c>
       <c r="M9" s="12" t="n">
         <v>4</v>
       </c>
-      <c r="N9" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="O9" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="P9" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q9" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="R9" s="5" t="n">
+      <c r="N9" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="O9" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="P9" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q9" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="R9" s="9" t="n">
         <v>0</v>
       </c>
       <c r="S9" s="12" t="n">
         <v>0</v>
       </c>
-      <c r="T9" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="U9" s="7" t="s">
-        <v>67</v>
-      </c>
-      <c r="V9" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="W9" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="X9" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y9" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z9" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA9" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB9" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC9" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD9" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE9" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF9" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG9" s="5" t="n">
+      <c r="T9" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="U9" s="11" t="s">
+        <v>68</v>
+      </c>
+      <c r="V9" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="W9" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="X9" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y9" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z9" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA9" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB9" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC9" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD9" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE9" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF9" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG9" s="9" t="n">
         <v>0</v>
       </c>
       <c r="AH9" s="12" t="n">
@@ -4624,22 +4662,22 @@
       <c r="AI9" s="12" t="n">
         <v>4</v>
       </c>
-      <c r="AJ9" s="5" t="n">
+      <c r="AJ9" s="9" t="n">
         <v>0</v>
       </c>
       <c r="AK9" s="14" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="B10" t="s">
         <v>21</v>
       </c>
-      <c r="C10" t="s">
-        <v>109</v>
+      <c r="C10" s="15" t="s">
+        <v>110</v>
       </c>
       <c r="D10" s="2" t="n">
         <v>209938195</v>
@@ -4741,18 +4779,18 @@
         <v>0</v>
       </c>
       <c r="AK10" s="15" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="B11" t="s">
         <v>22</v>
       </c>
-      <c r="C11" t="s">
-        <v>109</v>
+      <c r="C11" s="15" t="s">
+        <v>110</v>
       </c>
       <c r="D11" s="2" t="n">
         <v>218862170</v>
@@ -4854,18 +4892,18 @@
         <v>0</v>
       </c>
       <c r="AK11" s="15" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="B12" t="s">
         <v>23</v>
       </c>
-      <c r="C12" t="s">
-        <v>106</v>
+      <c r="C12" s="15" t="s">
+        <v>107</v>
       </c>
       <c r="D12" s="2" t="n">
         <v>188892440</v>
@@ -4919,7 +4957,7 @@
         <v>0</v>
       </c>
       <c r="U12" s="4" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="V12" s="3" t="n">
         <v>0</v>
@@ -4967,18 +5005,18 @@
         <v>0</v>
       </c>
       <c r="AK12" s="15" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="B13" t="s">
         <v>28</v>
       </c>
-      <c r="C13" t="s">
-        <v>106</v>
+      <c r="C13" s="15" t="s">
+        <v>107</v>
       </c>
       <c r="D13" s="2" t="n">
         <v>209040064</v>
@@ -5032,7 +5070,7 @@
         <v>0</v>
       </c>
       <c r="U13" s="4" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="V13" s="3" t="n">
         <v>0</v>
@@ -5080,18 +5118,18 @@
         <v>0</v>
       </c>
       <c r="AK13" s="15" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="B14" t="s">
         <v>25</v>
       </c>
-      <c r="C14" t="s">
-        <v>106</v>
+      <c r="C14" s="15" t="s">
+        <v>107</v>
       </c>
       <c r="D14" s="2" t="n">
         <v>185974368</v>
@@ -5193,18 +5231,18 @@
         <v>0</v>
       </c>
       <c r="AK14" s="15" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="B15" t="s">
         <v>26</v>
       </c>
-      <c r="C15" t="s">
-        <v>106</v>
+      <c r="C15" s="15" t="s">
+        <v>107</v>
       </c>
       <c r="D15" s="2" t="n">
         <v>193418216</v>
@@ -5258,7 +5296,7 @@
         <v>50008264</v>
       </c>
       <c r="U15" s="4" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="V15" s="3" t="n">
         <v>0.258549918586779</v>
@@ -5306,18 +5344,18 @@
         <v>0</v>
       </c>
       <c r="AK15" s="15" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="B16" t="s">
         <v>27</v>
       </c>
-      <c r="C16" t="s">
-        <v>106</v>
+      <c r="C16" s="15" t="s">
+        <v>107</v>
       </c>
       <c r="D16" s="2" t="n">
         <v>206927897</v>
@@ -5419,18 +5457,18 @@
         <v>0</v>
       </c>
       <c r="AK16" s="15" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="B17" t="s">
         <v>29</v>
       </c>
-      <c r="C17" t="s">
-        <v>106</v>
+      <c r="C17" s="15" t="s">
+        <v>107</v>
       </c>
       <c r="D17" s="2" t="n">
         <v>221898008</v>
@@ -5484,7 +5522,7 @@
         <v>62562949</v>
       </c>
       <c r="U17" s="4" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="V17" s="3" t="n">
         <v>0.281944617546995</v>
@@ -5532,18 +5570,18 @@
         <v>0</v>
       </c>
       <c r="AK17" s="15" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="B18" t="s">
         <v>30</v>
       </c>
-      <c r="C18" t="s">
-        <v>106</v>
+      <c r="C18" s="15" t="s">
+        <v>107</v>
       </c>
       <c r="D18" s="2" t="n">
         <v>212905591</v>
@@ -5597,7 +5635,7 @@
         <v>0</v>
       </c>
       <c r="U18" s="4" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="V18" s="3" t="n">
         <v>0</v>
@@ -5645,18 +5683,18 @@
         <v>0</v>
       </c>
       <c r="AK18" s="15" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="B19" t="s">
         <v>31</v>
       </c>
-      <c r="C19" t="s">
-        <v>106</v>
+      <c r="C19" s="15" t="s">
+        <v>107</v>
       </c>
       <c r="D19" s="2" t="n">
         <v>208374448</v>
@@ -5710,7 +5748,7 @@
         <v>1500000</v>
       </c>
       <c r="U19" s="4" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="V19" s="3" t="n">
         <v>0.00719857935748437</v>
@@ -5758,18 +5796,18 @@
         <v>0</v>
       </c>
       <c r="AK19" s="15" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="B20" t="s">
         <v>34</v>
       </c>
-      <c r="C20" t="s">
-        <v>129</v>
+      <c r="C20" s="15" t="s">
+        <v>130</v>
       </c>
       <c r="D20" s="2" t="n">
         <v>162005238</v>
@@ -5823,7 +5861,7 @@
         <v>0</v>
       </c>
       <c r="U20" s="4" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="V20" s="3" t="n">
         <v>0</v>
@@ -5871,18 +5909,18 @@
         <v>0</v>
       </c>
       <c r="AK20" s="15" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="B21" t="s">
         <v>33</v>
       </c>
-      <c r="C21" t="s">
-        <v>106</v>
+      <c r="C21" s="15" t="s">
+        <v>107</v>
       </c>
       <c r="D21" s="2" t="n">
         <v>168180838</v>
@@ -5984,18 +6022,18 @@
         <v>0</v>
       </c>
       <c r="AK21" s="15" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="B22" t="s">
         <v>32</v>
       </c>
-      <c r="C22" t="s">
-        <v>106</v>
+      <c r="C22" s="15" t="s">
+        <v>107</v>
       </c>
       <c r="D22" s="2" t="n">
         <v>190008051</v>
@@ -6049,7 +6087,7 @@
         <v>0</v>
       </c>
       <c r="U22" s="4" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="V22" s="3" t="n">
         <v>0</v>
@@ -6097,18 +6135,18 @@
         <v>0</v>
       </c>
       <c r="AK22" s="15" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="B23" t="s">
         <v>35</v>
       </c>
-      <c r="C23" t="s">
-        <v>106</v>
+      <c r="C23" s="15" t="s">
+        <v>107</v>
       </c>
       <c r="D23" s="2" t="n">
         <v>173128201</v>
@@ -6210,18 +6248,18 @@
         <v>0</v>
       </c>
       <c r="AK23" s="15" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="B24" t="s">
         <v>36</v>
       </c>
-      <c r="C24" t="s">
-        <v>134</v>
+      <c r="C24" s="15" t="s">
+        <v>135</v>
       </c>
       <c r="D24" s="2" t="n">
         <v>193090618</v>
@@ -6275,7 +6313,7 @@
         <v>0</v>
       </c>
       <c r="U24" s="4" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="V24" s="3" t="n">
         <v>0</v>
@@ -6323,18 +6361,18 @@
         <v>0</v>
       </c>
       <c r="AK24" s="15" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="B25" t="s">
         <v>38</v>
       </c>
-      <c r="C25" t="s">
-        <v>106</v>
+      <c r="C25" s="15" t="s">
+        <v>107</v>
       </c>
       <c r="D25" s="2" t="n">
         <v>216276818</v>
@@ -6388,7 +6426,7 @@
         <v>34646479.34</v>
       </c>
       <c r="U25" s="4" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="V25" s="3" t="n">
         <v>0.1601950669535</v>
@@ -6436,18 +6474,18 @@
         <v>0</v>
       </c>
       <c r="AK25" s="15" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="B26" t="s">
         <v>37</v>
       </c>
-      <c r="C26" t="s">
-        <v>106</v>
+      <c r="C26" s="15" t="s">
+        <v>107</v>
       </c>
       <c r="D26" s="2" t="n">
         <v>205907220</v>
@@ -6549,18 +6587,18 @@
         <v>0</v>
       </c>
       <c r="AK26" s="15" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="B27" t="s">
         <v>39</v>
       </c>
-      <c r="C27" t="s">
-        <v>106</v>
+      <c r="C27" s="15" t="s">
+        <v>107</v>
       </c>
       <c r="D27" s="2" t="n">
         <v>233509359</v>
@@ -6614,7 +6652,7 @@
         <v>0</v>
       </c>
       <c r="U27" s="4" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="V27" s="3" t="n">
         <v>0</v>
@@ -6662,18 +6700,18 @@
         <v>0</v>
       </c>
       <c r="AK27" s="15" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="B28" t="s">
         <v>46</v>
       </c>
-      <c r="C28" t="s">
-        <v>106</v>
+      <c r="C28" s="15" t="s">
+        <v>107</v>
       </c>
       <c r="D28" s="2" t="n">
         <v>213008356</v>
@@ -6727,7 +6765,7 @@
         <v>0</v>
       </c>
       <c r="U28" s="4" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="V28" s="3" t="n">
         <v>0</v>
@@ -6775,18 +6813,18 @@
         <v>0</v>
       </c>
       <c r="AK28" s="15" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="B29" t="s">
         <v>47</v>
       </c>
-      <c r="C29" t="s">
-        <v>134</v>
+      <c r="C29" s="15" t="s">
+        <v>135</v>
       </c>
       <c r="D29" s="2" t="n">
         <v>198936970</v>
@@ -6840,7 +6878,7 @@
         <v>0</v>
       </c>
       <c r="U29" s="4" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="V29" s="3" t="n">
         <v>0</v>
@@ -6888,18 +6926,18 @@
         <v>0</v>
       </c>
       <c r="AK29" s="15" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="B30" t="s">
         <v>40</v>
       </c>
-      <c r="C30" t="s">
-        <v>106</v>
+      <c r="C30" s="15" t="s">
+        <v>107</v>
       </c>
       <c r="D30" s="2" t="n">
         <v>218529075</v>
@@ -6953,7 +6991,7 @@
         <v>36619908.12</v>
       </c>
       <c r="U30" s="4" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="V30" s="3" t="n">
         <v>0.167574534967487</v>
@@ -7001,18 +7039,18 @@
         <v>0</v>
       </c>
       <c r="AK30" s="15" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="B31" t="s">
         <v>42</v>
       </c>
-      <c r="C31" t="s">
-        <v>106</v>
+      <c r="C31" s="15" t="s">
+        <v>107</v>
       </c>
       <c r="D31" s="2" t="n">
         <v>204016550</v>
@@ -7066,7 +7104,7 @@
         <v>17500000</v>
       </c>
       <c r="U31" s="4" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="V31" s="3" t="n">
         <v>0.0857773548273412</v>
@@ -7114,18 +7152,18 @@
         <v>0</v>
       </c>
       <c r="AK31" s="15" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="B32" t="s">
         <v>43</v>
       </c>
-      <c r="C32" t="s">
-        <v>106</v>
+      <c r="C32" s="15" t="s">
+        <v>107</v>
       </c>
       <c r="D32" s="2" t="n">
         <v>147250806</v>
@@ -7227,18 +7265,18 @@
         <v>0</v>
       </c>
       <c r="AK32" s="15" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="B33" t="s">
         <v>44</v>
       </c>
-      <c r="C33" t="s">
-        <v>134</v>
+      <c r="C33" s="15" t="s">
+        <v>135</v>
       </c>
       <c r="D33" s="2" t="n">
         <v>211484741</v>
@@ -7292,7 +7330,7 @@
         <v>0</v>
       </c>
       <c r="U33" s="4" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="V33" s="3" t="n">
         <v>0</v>
@@ -7340,18 +7378,18 @@
         <v>0</v>
       </c>
       <c r="AK33" s="15" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="B34" t="s">
         <v>41</v>
       </c>
-      <c r="C34" t="s">
-        <v>106</v>
+      <c r="C34" s="15" t="s">
+        <v>107</v>
       </c>
       <c r="D34" s="2" t="n">
         <v>179931608</v>
@@ -7453,18 +7491,18 @@
         <v>3455421</v>
       </c>
       <c r="AK34" s="15" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="B35" t="s">
         <v>45</v>
       </c>
-      <c r="C35" t="s">
-        <v>106</v>
+      <c r="C35" s="15" t="s">
+        <v>107</v>
       </c>
       <c r="D35" s="2" t="n">
         <v>212058208</v>
@@ -7518,7 +7556,7 @@
         <v>47358790.79</v>
       </c>
       <c r="U35" s="4" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="V35" s="3" t="n">
         <v>0.223329203979692</v>
@@ -7566,18 +7604,18 @@
         <v>0</v>
       </c>
       <c r="AK35" s="15" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="B36" t="s">
         <v>48</v>
       </c>
-      <c r="C36" t="s">
-        <v>106</v>
+      <c r="C36" s="15" t="s">
+        <v>107</v>
       </c>
       <c r="D36" s="2" t="n">
         <v>202030262</v>
@@ -7679,18 +7717,18 @@
         <v>0</v>
       </c>
       <c r="AK36" s="15" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="B37" t="s">
         <v>49</v>
       </c>
-      <c r="C37" t="s">
-        <v>106</v>
+      <c r="C37" s="15" t="s">
+        <v>107</v>
       </c>
       <c r="D37" s="2" t="n">
         <v>223476949</v>
@@ -7744,7 +7782,7 @@
         <v>33403159.16</v>
       </c>
       <c r="U37" s="4" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="V37" s="3" t="n">
         <v>0.149470266662715</v>
@@ -7792,18 +7830,18 @@
         <v>0</v>
       </c>
       <c r="AK37" s="15" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="B38" t="s">
         <v>50</v>
       </c>
-      <c r="C38" t="s">
-        <v>106</v>
+      <c r="C38" s="15" t="s">
+        <v>107</v>
       </c>
       <c r="D38" s="2" t="n">
         <v>197271578</v>
@@ -7905,18 +7943,18 @@
         <v>0</v>
       </c>
       <c r="AK38" s="15" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="B39" t="s">
         <v>51</v>
       </c>
-      <c r="C39" t="s">
-        <v>106</v>
+      <c r="C39" s="15" t="s">
+        <v>107</v>
       </c>
       <c r="D39" s="2" t="n">
         <v>193294054</v>
@@ -7970,7 +8008,7 @@
         <v>27112688</v>
       </c>
       <c r="U39" s="4" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="V39" s="3" t="n">
         <v>0.140266539186974</v>
@@ -8018,18 +8056,18 @@
         <v>0</v>
       </c>
       <c r="AK39" s="15" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="B40" t="s">
         <v>52</v>
       </c>
-      <c r="C40" t="s">
-        <v>112</v>
+      <c r="C40" s="15" t="s">
+        <v>113</v>
       </c>
       <c r="D40" s="2" t="n">
         <v>156169931</v>
@@ -8131,18 +8169,18 @@
         <v>0</v>
       </c>
       <c r="AK40" s="15" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="B41" t="s">
         <v>54</v>
       </c>
-      <c r="C41" t="s">
-        <v>106</v>
+      <c r="C41" s="15" t="s">
+        <v>107</v>
       </c>
       <c r="D41" s="2" t="n">
         <v>200030252</v>
@@ -8244,18 +8282,18 @@
         <v>0</v>
       </c>
       <c r="AK41" s="15" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="B42" t="s">
         <v>55</v>
       </c>
-      <c r="C42" t="s">
-        <v>106</v>
+      <c r="C42" s="15" t="s">
+        <v>107</v>
       </c>
       <c r="D42" s="2" t="n">
         <v>189477607</v>
@@ -8357,18 +8395,18 @@
         <v>0</v>
       </c>
       <c r="AK42" s="15" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="B43" t="s">
         <v>56</v>
       </c>
-      <c r="C43" t="s">
-        <v>106</v>
+      <c r="C43" s="15" t="s">
+        <v>107</v>
       </c>
       <c r="D43" s="2" t="n">
         <v>206888882</v>
@@ -8422,7 +8460,7 @@
         <v>0</v>
       </c>
       <c r="U43" s="4" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="V43" s="3" t="n">
         <v>0</v>
@@ -8470,18 +8508,18 @@
         <v>0</v>
       </c>
       <c r="AK43" s="15" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="B44" t="s">
         <v>57</v>
       </c>
-      <c r="C44" t="s">
-        <v>106</v>
+      <c r="C44" s="15" t="s">
+        <v>107</v>
       </c>
       <c r="D44" s="2" t="n">
         <v>281319361</v>
@@ -8583,18 +8621,18 @@
         <v>509936.5</v>
       </c>
       <c r="AK44" s="15" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="B45" t="s">
         <v>58</v>
       </c>
-      <c r="C45" t="s">
-        <v>112</v>
+      <c r="C45" s="15" t="s">
+        <v>113</v>
       </c>
       <c r="D45" s="2" t="n">
         <v>195743566</v>
@@ -8648,7 +8686,7 @@
         <v>0</v>
       </c>
       <c r="U45" s="4" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="V45" s="3" t="n">
         <v>0</v>
@@ -8696,18 +8734,18 @@
         <v>0</v>
       </c>
       <c r="AK45" s="15" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="B46" t="s">
         <v>60</v>
       </c>
-      <c r="C46" t="s">
-        <v>106</v>
+      <c r="C46" s="15" t="s">
+        <v>107</v>
       </c>
       <c r="D46" s="2" t="n">
         <v>189544888</v>
@@ -8761,7 +8799,7 @@
         <v>12031000</v>
       </c>
       <c r="U46" s="4" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="V46" s="3" t="n">
         <v>0.0634730913977485</v>
@@ -8809,18 +8847,18 @@
         <v>0</v>
       </c>
       <c r="AK46" s="15" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="B47" t="s">
         <v>59</v>
       </c>
-      <c r="C47" t="s">
-        <v>106</v>
+      <c r="C47" s="15" t="s">
+        <v>107</v>
       </c>
       <c r="D47" s="2" t="n">
         <v>195053740</v>
@@ -8922,18 +8960,18 @@
         <v>0</v>
       </c>
       <c r="AK47" s="15" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="B48" t="s">
         <v>61</v>
       </c>
-      <c r="C48" t="s">
-        <v>106</v>
+      <c r="C48" s="15" t="s">
+        <v>107</v>
       </c>
       <c r="D48" s="2" t="n">
         <v>181257515</v>
@@ -8987,7 +9025,7 @@
         <v>57170000</v>
       </c>
       <c r="U48" s="4" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="V48" s="3" t="n">
         <v>0.315407612203003</v>
@@ -9035,18 +9073,18 @@
         <v>0</v>
       </c>
       <c r="AK48" s="15" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="B49" t="s">
         <v>63</v>
       </c>
-      <c r="C49" t="s">
-        <v>134</v>
+      <c r="C49" s="15" t="s">
+        <v>135</v>
       </c>
       <c r="D49" s="2" t="n">
         <v>203670005</v>
@@ -9100,7 +9138,7 @@
         <v>0</v>
       </c>
       <c r="U49" s="4" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="V49" s="3" t="n">
         <v>0</v>
@@ -9148,18 +9186,18 @@
         <v>0</v>
       </c>
       <c r="AK49" s="15" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="B50" t="s">
         <v>62</v>
       </c>
-      <c r="C50" t="s">
-        <v>106</v>
+      <c r="C50" s="15" t="s">
+        <v>107</v>
       </c>
       <c r="D50" s="2" t="n">
         <v>199476099</v>
@@ -9213,7 +9251,7 @@
         <v>6324000</v>
       </c>
       <c r="U50" s="4" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="V50" s="3" t="n">
         <v>0.0317030462882673</v>
@@ -9261,18 +9299,18 @@
         <v>0</v>
       </c>
       <c r="AK50" s="15" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="B51" t="s">
         <v>64</v>
       </c>
-      <c r="C51" t="s">
-        <v>106</v>
+      <c r="C51" s="15" t="s">
+        <v>107</v>
       </c>
       <c r="D51" s="2" t="n">
         <v>205004743</v>
@@ -9374,120 +9412,233 @@
         <v>0</v>
       </c>
       <c r="AK51" s="15" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
     </row>
     <row r="52">
-      <c r="A52" s="11" t="s">
-        <v>162</v>
-      </c>
-      <c r="B52" s="11" t="s">
+      <c r="A52" s="8" t="s">
+        <v>163</v>
+      </c>
+      <c r="B52" s="8" t="s">
         <v>65</v>
       </c>
-      <c r="C52" s="11" t="s">
-        <v>163</v>
-      </c>
-      <c r="D52" s="8" t="n">
+      <c r="C52" s="13" t="s">
+        <v>164</v>
+      </c>
+      <c r="D52" s="5" t="n">
         <v>10000000003</v>
       </c>
-      <c r="E52" s="11" t="n">
+      <c r="E52" s="8" t="n">
         <v>61</v>
       </c>
-      <c r="F52" s="11" t="n">
+      <c r="F52" s="8" t="n">
         <v>4402</v>
       </c>
-      <c r="G52" s="11" t="n">
+      <c r="G52" s="8" t="n">
         <v>3610</v>
       </c>
-      <c r="H52" s="8" t="n">
+      <c r="H52" s="5" t="n">
         <v>3708434674.31</v>
       </c>
-      <c r="I52" s="8" t="n">
+      <c r="I52" s="5" t="n">
         <v>463299728</v>
       </c>
-      <c r="J52" s="8" t="n">
+      <c r="J52" s="5" t="n">
         <v>4171734402.31</v>
       </c>
-      <c r="K52" s="9" t="n">
+      <c r="K52" s="6" t="n">
         <v>0.417173440105848</v>
       </c>
-      <c r="L52" s="8" t="n">
+      <c r="L52" s="5" t="n">
         <v>1435192267.66</v>
       </c>
-      <c r="M52" s="11" t="n">
+      <c r="M52" s="8" t="n">
         <v>1867</v>
       </c>
-      <c r="N52" s="8" t="n">
+      <c r="N52" s="5" t="n">
         <v>1780528970.9</v>
       </c>
-      <c r="O52" s="8" t="n">
+      <c r="O52" s="5" t="n">
         <v>224694444.87</v>
       </c>
-      <c r="P52" s="8" t="n">
+      <c r="P52" s="5" t="n">
         <v>168359444.87</v>
       </c>
-      <c r="Q52" s="8" t="n">
+      <c r="Q52" s="5" t="n">
         <v>38835000</v>
       </c>
-      <c r="R52" s="8" t="n">
+      <c r="R52" s="5" t="n">
         <v>17500000</v>
       </c>
-      <c r="S52" s="11" t="n">
+      <c r="S52" s="8" t="n">
         <v>534</v>
       </c>
-      <c r="T52" s="8" t="n">
+      <c r="T52" s="5" t="n">
         <v>2005223415.77</v>
       </c>
-      <c r="U52" s="10" t="s">
+      <c r="U52" s="7" t="s">
+        <v>68</v>
+      </c>
+      <c r="V52" s="6" t="n">
+        <v>0.200522341516843</v>
+      </c>
+      <c r="W52" s="5" t="n">
+        <v>1731421723.08</v>
+      </c>
+      <c r="X52" s="5" t="n">
+        <v>86555171.43</v>
+      </c>
+      <c r="Y52" s="5" t="n">
+        <v>69323109.17</v>
+      </c>
+      <c r="Z52" s="5" t="n">
+        <v>737578902.24</v>
+      </c>
+      <c r="AA52" s="5" t="n">
+        <v>171816601.6</v>
+      </c>
+      <c r="AB52" s="5" t="n">
+        <v>22781325.76</v>
+      </c>
+      <c r="AC52" s="5" t="n">
+        <v>65107273.31</v>
+      </c>
+      <c r="AD52" s="5" t="n">
+        <v>237380398.25</v>
+      </c>
+      <c r="AE52" s="5" t="n">
+        <v>430533135.95</v>
+      </c>
+      <c r="AF52" s="5" t="n">
+        <v>549250719.56</v>
+      </c>
+      <c r="AG52" s="5" t="n">
+        <v>397130545.99</v>
+      </c>
+      <c r="AH52" s="8" t="n">
+        <v>269</v>
+      </c>
+      <c r="AI52" s="8" t="n">
+        <v>373</v>
+      </c>
+      <c r="AJ52" s="5" t="n">
+        <v>3965357.5</v>
+      </c>
+      <c r="AK52" s="13" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="8" t="s">
+        <v>165</v>
+      </c>
+      <c r="B53" s="8" t="s">
         <v>67</v>
       </c>
-      <c r="V52" s="9" t="n">
-        <v>0.200522341516843</v>
-      </c>
-      <c r="W52" s="8" t="n">
-        <v>1731421723.08</v>
-      </c>
-      <c r="X52" s="8" t="n">
-        <v>86555171.43</v>
-      </c>
-      <c r="Y52" s="8" t="n">
-        <v>69323109.17</v>
-      </c>
-      <c r="Z52" s="8" t="n">
-        <v>737578902.24</v>
-      </c>
-      <c r="AA52" s="8" t="n">
-        <v>171816601.6</v>
-      </c>
-      <c r="AB52" s="8" t="n">
-        <v>22781325.76</v>
-      </c>
-      <c r="AC52" s="8" t="n">
-        <v>65107273.31</v>
-      </c>
-      <c r="AD52" s="8" t="n">
-        <v>237380398.25</v>
-      </c>
-      <c r="AE52" s="8" t="n">
-        <v>430533135.95</v>
-      </c>
-      <c r="AF52" s="8" t="n">
-        <v>549250719.56</v>
-      </c>
-      <c r="AG52" s="8" t="n">
-        <v>397130545.99</v>
-      </c>
-      <c r="AH52" s="11" t="n">
-        <v>269</v>
-      </c>
-      <c r="AI52" s="11" t="n">
-        <v>373</v>
-      </c>
-      <c r="AJ52" s="8" t="n">
+      <c r="C53" s="13" t="s">
+        <v>166</v>
+      </c>
+      <c r="D53" s="5" t="n">
+        <v>4440562268</v>
+      </c>
+      <c r="E53" s="8" t="n">
+        <v>29</v>
+      </c>
+      <c r="F53" s="8" t="n">
+        <v>3441</v>
+      </c>
+      <c r="G53" s="8" t="n">
+        <v>3125</v>
+      </c>
+      <c r="H53" s="5" t="n">
+        <v>3028965541.22</v>
+      </c>
+      <c r="I53" s="5" t="n">
+        <v>412603520</v>
+      </c>
+      <c r="J53" s="5" t="n">
+        <v>3441569061.22</v>
+      </c>
+      <c r="K53" s="6" t="n">
+        <v>0.775030019513736</v>
+      </c>
+      <c r="L53" s="5" t="n">
+        <v>1385478477.61</v>
+      </c>
+      <c r="M53" s="8" t="n">
+        <v>1355</v>
+      </c>
+      <c r="N53" s="5" t="n">
+        <v>1446728679.7</v>
+      </c>
+      <c r="O53" s="5" t="n">
+        <v>126257497.66</v>
+      </c>
+      <c r="P53" s="5" t="n">
+        <v>87422497.66</v>
+      </c>
+      <c r="Q53" s="5" t="n">
+        <v>38835000</v>
+      </c>
+      <c r="R53" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="S53" s="8" t="n">
+        <v>438</v>
+      </c>
+      <c r="T53" s="5" t="n">
+        <v>1572986177.36</v>
+      </c>
+      <c r="U53" s="6" t="n">
+        <v>0.45705495062836</v>
+      </c>
+      <c r="V53" s="6" t="n">
+        <v>0.354231307304348</v>
+      </c>
+      <c r="W53" s="5" t="n">
+        <v>1451104633.38</v>
+      </c>
+      <c r="X53" s="5" t="n">
+        <v>54748315.31</v>
+      </c>
+      <c r="Y53" s="5" t="n">
+        <v>15839907.67</v>
+      </c>
+      <c r="Z53" s="5" t="n">
+        <v>710051173.87</v>
+      </c>
+      <c r="AA53" s="5" t="n">
+        <v>52746543.98</v>
+      </c>
+      <c r="AB53" s="5" t="n">
+        <v>15839907.67</v>
+      </c>
+      <c r="AC53" s="5" t="n">
+        <v>55305273.31</v>
+      </c>
+      <c r="AD53" s="5" t="n">
+        <v>126762455.53</v>
+      </c>
+      <c r="AE53" s="5" t="n">
+        <v>253328337.11</v>
+      </c>
+      <c r="AF53" s="5" t="n">
+        <v>512424850.1</v>
+      </c>
+      <c r="AG53" s="5" t="n">
+        <v>361554676.53</v>
+      </c>
+      <c r="AH53" s="8" t="n">
+        <v>103</v>
+      </c>
+      <c r="AI53" s="8" t="n">
+        <v>108</v>
+      </c>
+      <c r="AJ53" s="5" t="n">
         <v>3965357.5</v>
       </c>
-      <c r="AK52" s="13" t="s">
-        <v>117</v>
+      <c r="AK53" s="13" t="s">
+        <v>108</v>
       </c>
     </row>
   </sheetData>
@@ -9508,585 +9659,585 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
-        <v>164</v>
+        <v>167</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>165</v>
+        <v>168</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>166</v>
+        <v>169</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="s">
-        <v>167</v>
+        <v>170</v>
       </c>
       <c r="B2" t="s">
         <v>0</v>
       </c>
       <c r="C2" s="15" t="s">
-        <v>168</v>
+        <v>171</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="s">
-        <v>167</v>
+        <v>170</v>
       </c>
       <c r="B3" t="s">
         <v>1</v>
       </c>
       <c r="C3" s="15" t="s">
-        <v>169</v>
+        <v>172</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="s">
-        <v>167</v>
+        <v>170</v>
       </c>
       <c r="B4" t="s">
         <v>2</v>
       </c>
       <c r="C4" s="15" t="s">
-        <v>170</v>
+        <v>173</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="s">
-        <v>167</v>
+        <v>170</v>
       </c>
       <c r="B5" t="s">
         <v>3</v>
       </c>
       <c r="C5" s="15" t="s">
-        <v>171</v>
+        <v>174</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="s">
-        <v>167</v>
+        <v>170</v>
       </c>
       <c r="B6" t="s">
         <v>4</v>
       </c>
       <c r="C6" s="15" t="s">
-        <v>172</v>
+        <v>175</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="s">
-        <v>167</v>
+        <v>170</v>
       </c>
       <c r="B7" t="s">
         <v>5</v>
       </c>
       <c r="C7" s="15" t="s">
-        <v>173</v>
+        <v>176</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="s">
-        <v>167</v>
+        <v>170</v>
       </c>
       <c r="B8" t="s">
         <v>6</v>
       </c>
       <c r="C8" s="15" t="s">
-        <v>174</v>
+        <v>177</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="s">
-        <v>167</v>
+        <v>170</v>
       </c>
       <c r="B9" t="s">
         <v>7</v>
       </c>
       <c r="C9" s="15" t="s">
-        <v>175</v>
+        <v>178</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="s">
-        <v>167</v>
+        <v>170</v>
       </c>
       <c r="B10" t="s">
         <v>8</v>
       </c>
       <c r="C10" s="15" t="s">
-        <v>176</v>
+        <v>179</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="s">
-        <v>167</v>
+        <v>170</v>
       </c>
       <c r="B11" t="s">
         <v>9</v>
       </c>
       <c r="C11" s="15" t="s">
-        <v>177</v>
+        <v>180</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="s">
-        <v>178</v>
+        <v>181</v>
       </c>
       <c r="B12" t="s">
         <v>11</v>
       </c>
       <c r="C12" s="15" t="s">
-        <v>179</v>
+        <v>182</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="s">
-        <v>178</v>
+        <v>181</v>
       </c>
       <c r="B13" t="s">
         <v>53</v>
       </c>
       <c r="C13" s="15" t="s">
-        <v>180</v>
+        <v>183</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="s">
-        <v>178</v>
+        <v>181</v>
       </c>
       <c r="B14" t="s">
         <v>13</v>
       </c>
       <c r="C14" s="15" t="s">
-        <v>181</v>
+        <v>184</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="s">
-        <v>178</v>
+        <v>181</v>
       </c>
       <c r="B15" t="s">
         <v>24</v>
       </c>
       <c r="C15" s="15" t="s">
-        <v>182</v>
+        <v>185</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="s">
-        <v>178</v>
+        <v>181</v>
       </c>
       <c r="B16" t="s">
         <v>15</v>
       </c>
       <c r="C16" s="15" t="s">
-        <v>183</v>
+        <v>186</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="s">
-        <v>184</v>
+        <v>187</v>
       </c>
       <c r="B17" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="C17" s="15" t="s">
-        <v>185</v>
+        <v>188</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="s">
-        <v>184</v>
+        <v>187</v>
       </c>
       <c r="B18" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="C18" s="15" t="s">
-        <v>186</v>
+        <v>189</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="s">
-        <v>184</v>
+        <v>187</v>
       </c>
       <c r="B19" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="C19" s="15" t="s">
-        <v>187</v>
+        <v>190</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="s">
-        <v>184</v>
+        <v>187</v>
       </c>
       <c r="B20" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="C20" s="15" t="s">
-        <v>188</v>
+        <v>191</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="s">
-        <v>184</v>
+        <v>187</v>
       </c>
       <c r="B21" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="C21" s="15" t="s">
-        <v>189</v>
+        <v>192</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="s">
-        <v>184</v>
+        <v>187</v>
       </c>
       <c r="B22" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="C22" s="15" t="s">
-        <v>190</v>
+        <v>193</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="s">
-        <v>184</v>
+        <v>187</v>
       </c>
       <c r="B23" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="C23" s="15" t="s">
-        <v>191</v>
+        <v>194</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="s">
-        <v>184</v>
+        <v>187</v>
       </c>
       <c r="B24" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="C24" s="15" t="s">
-        <v>192</v>
+        <v>195</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="s">
-        <v>184</v>
+        <v>187</v>
       </c>
       <c r="B25" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="C25" s="15" t="s">
-        <v>193</v>
+        <v>196</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="s">
-        <v>184</v>
+        <v>187</v>
       </c>
       <c r="B26" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="C26" s="15" t="s">
-        <v>194</v>
+        <v>197</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="s">
-        <v>184</v>
+        <v>187</v>
       </c>
       <c r="B27" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="C27" s="15" t="s">
-        <v>195</v>
+        <v>198</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="s">
-        <v>184</v>
+        <v>187</v>
       </c>
       <c r="B28" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="C28" s="15" t="s">
-        <v>196</v>
+        <v>199</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="s">
-        <v>184</v>
+        <v>187</v>
       </c>
       <c r="B29" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="C29" s="15" t="s">
-        <v>197</v>
+        <v>200</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="s">
-        <v>184</v>
+        <v>187</v>
       </c>
       <c r="B30" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="C30" s="15" t="s">
-        <v>198</v>
+        <v>201</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="s">
-        <v>184</v>
+        <v>187</v>
       </c>
       <c r="B31" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="C31" s="15" t="s">
-        <v>199</v>
+        <v>202</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="s">
-        <v>184</v>
+        <v>187</v>
       </c>
       <c r="B32" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="C32" s="15" t="s">
-        <v>200</v>
+        <v>203</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="s">
-        <v>184</v>
+        <v>187</v>
       </c>
       <c r="B33" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="C33" s="15" t="s">
-        <v>201</v>
+        <v>204</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="s">
-        <v>184</v>
+        <v>187</v>
       </c>
       <c r="B34" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="C34" s="15" t="s">
-        <v>202</v>
+        <v>205</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="s">
-        <v>184</v>
+        <v>187</v>
       </c>
       <c r="B35" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="C35" s="15" t="s">
-        <v>203</v>
+        <v>206</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="s">
-        <v>184</v>
+        <v>187</v>
       </c>
       <c r="B36" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="C36" s="15" t="s">
-        <v>204</v>
+        <v>207</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="s">
-        <v>184</v>
+        <v>187</v>
       </c>
       <c r="B37" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="C37" s="15" t="s">
-        <v>205</v>
+        <v>208</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="s">
-        <v>184</v>
+        <v>187</v>
       </c>
       <c r="B38" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="C38" s="15" t="s">
-        <v>206</v>
+        <v>209</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="s">
-        <v>184</v>
+        <v>187</v>
       </c>
       <c r="B39" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="C39" s="15" t="s">
-        <v>207</v>
+        <v>210</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="s">
-        <v>184</v>
+        <v>187</v>
       </c>
       <c r="B40" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="C40" s="15" t="s">
-        <v>208</v>
+        <v>211</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="s">
-        <v>184</v>
+        <v>187</v>
       </c>
       <c r="B41" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="C41" s="15" t="s">
-        <v>209</v>
+        <v>212</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="s">
-        <v>184</v>
+        <v>187</v>
       </c>
       <c r="B42" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="C42" s="15" t="s">
-        <v>210</v>
+        <v>213</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="s">
-        <v>184</v>
+        <v>187</v>
       </c>
       <c r="B43" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="C43" s="15" t="s">
-        <v>211</v>
+        <v>214</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="s">
-        <v>184</v>
+        <v>187</v>
       </c>
       <c r="B44" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="C44" s="15" t="s">
-        <v>212</v>
+        <v>215</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="s">
-        <v>184</v>
+        <v>187</v>
       </c>
       <c r="B45" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="C45" s="15" t="s">
-        <v>213</v>
+        <v>216</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="s">
-        <v>184</v>
+        <v>187</v>
       </c>
       <c r="B46" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="C46" s="15" t="s">
-        <v>214</v>
+        <v>217</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="s">
-        <v>184</v>
+        <v>187</v>
       </c>
       <c r="B47" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="C47" s="15" t="s">
-        <v>215</v>
+        <v>218</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="s">
-        <v>184</v>
+        <v>187</v>
       </c>
       <c r="B48" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="C48" s="15" t="s">
-        <v>216</v>
+        <v>219</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="s">
-        <v>184</v>
+        <v>187</v>
       </c>
       <c r="B49" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="C49" s="15" t="s">
-        <v>217</v>
+        <v>220</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="s">
-        <v>184</v>
+        <v>187</v>
       </c>
       <c r="B50" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="C50" s="15" t="s">
-        <v>218</v>
+        <v>221</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="s">
-        <v>184</v>
+        <v>187</v>
       </c>
       <c r="B51" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="C51" s="15" t="s">
-        <v>219</v>
+        <v>222</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="s">
-        <v>184</v>
+        <v>187</v>
       </c>
       <c r="B52" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="C52" s="15" t="s">
-        <v>220</v>
+        <v>223</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="s">
-        <v>184</v>
+        <v>187</v>
       </c>
       <c r="B53" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="C53" s="15" t="s">
-        <v>221</v>
+        <v>224</v>
       </c>
     </row>
   </sheetData>
@@ -10105,77 +10256,82 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
-        <v>222</v>
+        <v>225</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="15" t="s">
-        <v>223</v>
+        <v>226</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="15" t="s">
-        <v>224</v>
+        <v>227</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="15" t="s">
-        <v>225</v>
+        <v>228</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="15" t="s">
-        <v>226</v>
+        <v>229</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="15" t="s">
-        <v>227</v>
+        <v>230</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="15" t="s">
-        <v>228</v>
+        <v>231</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="15" t="s">
-        <v>229</v>
+        <v>232</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="15" t="s">
-        <v>230</v>
+        <v>233</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="15" t="s">
-        <v>231</v>
+        <v>234</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="15" t="s">
-        <v>232</v>
+        <v>235</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="15" t="s">
-        <v>233</v>
+        <v>236</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="15" t="s">
-        <v>234</v>
+        <v>237</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="15" t="s">
-        <v>235</v>
+        <v>238</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="15" t="s">
-        <v>236</v>
+        <v>239</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="15" t="s">
+        <v>240</v>
       </c>
     </row>
   </sheetData>
@@ -10201,1328 +10357,1328 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>237</v>
+        <v>241</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>238</v>
+        <v>242</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>239</v>
+        <v>243</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>240</v>
+        <v>244</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>241</v>
+        <v>245</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>242</v>
+        <v>246</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="15" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="B2" s="15" t="s">
-        <v>243</v>
+        <v>247</v>
       </c>
       <c r="C2" s="15" t="s">
-        <v>244</v>
+        <v>248</v>
       </c>
       <c r="D2" s="15" t="s">
-        <v>245</v>
+        <v>249</v>
       </c>
       <c r="E2" s="15" t="s">
-        <v>246</v>
+        <v>250</v>
       </c>
       <c r="F2" s="15" t="s">
-        <v>247</v>
+        <v>251</v>
       </c>
       <c r="G2" s="15" t="s">
-        <v>248</v>
+        <v>252</v>
       </c>
       <c r="H2" s="15" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="15" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="B3" s="15" t="s">
-        <v>249</v>
+        <v>253</v>
       </c>
       <c r="C3" s="15" t="s">
-        <v>250</v>
+        <v>254</v>
       </c>
       <c r="D3" s="15" t="s">
-        <v>251</v>
+        <v>255</v>
       </c>
       <c r="E3" s="15" t="s">
-        <v>252</v>
+        <v>256</v>
       </c>
       <c r="F3" s="15" t="s">
-        <v>253</v>
+        <v>257</v>
       </c>
       <c r="G3" s="15" t="s">
-        <v>254</v>
+        <v>258</v>
       </c>
       <c r="H3" s="15" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="15" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="B4" s="15" t="s">
-        <v>255</v>
+        <v>259</v>
       </c>
       <c r="C4" s="15" t="s">
-        <v>256</v>
+        <v>260</v>
       </c>
       <c r="D4" s="15" t="s">
-        <v>257</v>
+        <v>261</v>
       </c>
       <c r="E4" s="15" t="s">
-        <v>258</v>
+        <v>262</v>
       </c>
       <c r="F4" s="15" t="s">
-        <v>259</v>
+        <v>263</v>
       </c>
       <c r="G4" s="15" t="s">
-        <v>260</v>
+        <v>264</v>
       </c>
       <c r="H4" s="15" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="15" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="B5" s="15" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="C5" s="15" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="D5" s="15" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="E5" s="15" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="F5" s="15" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="G5" s="15" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="H5" s="15" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="15" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="B6" s="15" t="s">
-        <v>261</v>
+        <v>265</v>
       </c>
       <c r="C6" s="15" t="s">
-        <v>262</v>
+        <v>266</v>
       </c>
       <c r="D6" s="15" t="s">
-        <v>263</v>
+        <v>267</v>
       </c>
       <c r="E6" s="15" t="s">
-        <v>264</v>
+        <v>268</v>
       </c>
       <c r="F6" s="15" t="s">
-        <v>264</v>
+        <v>268</v>
       </c>
       <c r="G6" s="15" t="s">
-        <v>265</v>
+        <v>269</v>
       </c>
       <c r="H6" s="15" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="15" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="B7" s="15" t="s">
-        <v>266</v>
+        <v>270</v>
       </c>
       <c r="C7" s="15" t="s">
-        <v>267</v>
+        <v>271</v>
       </c>
       <c r="D7" s="15" t="s">
-        <v>268</v>
+        <v>272</v>
       </c>
       <c r="E7" s="15" t="s">
-        <v>269</v>
+        <v>273</v>
       </c>
       <c r="F7" s="15" t="s">
-        <v>270</v>
+        <v>274</v>
       </c>
       <c r="G7" s="15" t="s">
-        <v>271</v>
+        <v>275</v>
       </c>
       <c r="H7" s="15" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="15" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="B8" s="15" t="s">
-        <v>272</v>
+        <v>276</v>
       </c>
       <c r="C8" s="15" t="s">
-        <v>273</v>
+        <v>277</v>
       </c>
       <c r="D8" s="15" t="s">
-        <v>274</v>
+        <v>278</v>
       </c>
       <c r="E8" s="15" t="s">
-        <v>275</v>
+        <v>279</v>
       </c>
       <c r="F8" s="15" t="s">
-        <v>275</v>
+        <v>279</v>
       </c>
       <c r="G8" s="15" t="s">
-        <v>276</v>
+        <v>280</v>
       </c>
       <c r="H8" s="15" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="14" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="B9" s="14" t="s">
-        <v>277</v>
+        <v>281</v>
       </c>
       <c r="C9" s="14" t="s">
-        <v>278</v>
+        <v>282</v>
       </c>
       <c r="D9" s="14" t="s">
-        <v>279</v>
+        <v>283</v>
       </c>
       <c r="E9" s="14" t="s">
-        <v>280</v>
+        <v>284</v>
       </c>
       <c r="F9" s="14" t="s">
-        <v>281</v>
+        <v>285</v>
       </c>
       <c r="G9" s="14" t="s">
-        <v>282</v>
+        <v>286</v>
       </c>
       <c r="H9" s="14" t="s">
-        <v>283</v>
+        <v>287</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="15" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="B10" s="15" t="s">
-        <v>284</v>
+        <v>288</v>
       </c>
       <c r="C10" s="15" t="s">
-        <v>285</v>
+        <v>289</v>
       </c>
       <c r="D10" s="15" t="s">
-        <v>286</v>
+        <v>290</v>
       </c>
       <c r="E10" s="15" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="F10" s="15" t="s">
-        <v>287</v>
+        <v>291</v>
       </c>
       <c r="G10" s="15" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="H10" s="15" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="15" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="B11" s="15" t="s">
-        <v>288</v>
+        <v>292</v>
       </c>
       <c r="C11" s="15" t="s">
-        <v>289</v>
+        <v>293</v>
       </c>
       <c r="D11" s="15" t="s">
-        <v>290</v>
+        <v>294</v>
       </c>
       <c r="E11" s="15" t="s">
-        <v>291</v>
+        <v>295</v>
       </c>
       <c r="F11" s="15" t="s">
-        <v>292</v>
+        <v>296</v>
       </c>
       <c r="G11" s="15" t="s">
-        <v>293</v>
+        <v>297</v>
       </c>
       <c r="H11" s="15" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="15" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="B12" s="15" t="s">
-        <v>294</v>
+        <v>298</v>
       </c>
       <c r="C12" s="15" t="s">
-        <v>295</v>
+        <v>299</v>
       </c>
       <c r="D12" s="15" t="s">
-        <v>296</v>
+        <v>300</v>
       </c>
       <c r="E12" s="15" t="s">
-        <v>297</v>
+        <v>301</v>
       </c>
       <c r="F12" s="15" t="s">
-        <v>297</v>
+        <v>301</v>
       </c>
       <c r="G12" s="15" t="s">
-        <v>298</v>
+        <v>302</v>
       </c>
       <c r="H12" s="15" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="15" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="B13" s="15" t="s">
-        <v>299</v>
+        <v>303</v>
       </c>
       <c r="C13" s="15" t="s">
-        <v>300</v>
+        <v>304</v>
       </c>
       <c r="D13" s="15" t="s">
-        <v>301</v>
+        <v>305</v>
       </c>
       <c r="E13" s="15" t="s">
-        <v>302</v>
+        <v>306</v>
       </c>
       <c r="F13" s="15" t="s">
-        <v>303</v>
+        <v>307</v>
       </c>
       <c r="G13" s="15" t="s">
-        <v>304</v>
+        <v>308</v>
       </c>
       <c r="H13" s="15" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="15" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="B14" s="15" t="s">
-        <v>305</v>
+        <v>309</v>
       </c>
       <c r="C14" s="15" t="s">
-        <v>306</v>
+        <v>310</v>
       </c>
       <c r="D14" s="15" t="s">
-        <v>307</v>
+        <v>311</v>
       </c>
       <c r="E14" s="15" t="s">
-        <v>308</v>
+        <v>312</v>
       </c>
       <c r="F14" s="15" t="s">
-        <v>309</v>
+        <v>313</v>
       </c>
       <c r="G14" s="15" t="s">
-        <v>310</v>
+        <v>314</v>
       </c>
       <c r="H14" s="15" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="15" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="B15" s="15" t="s">
-        <v>311</v>
+        <v>315</v>
       </c>
       <c r="C15" s="15" t="s">
-        <v>312</v>
+        <v>316</v>
       </c>
       <c r="D15" s="15" t="s">
-        <v>313</v>
+        <v>317</v>
       </c>
       <c r="E15" s="15" t="s">
-        <v>314</v>
+        <v>318</v>
       </c>
       <c r="F15" s="15" t="s">
-        <v>315</v>
+        <v>319</v>
       </c>
       <c r="G15" s="15" t="s">
-        <v>316</v>
+        <v>320</v>
       </c>
       <c r="H15" s="15" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="15" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="B16" s="15" t="s">
-        <v>317</v>
+        <v>321</v>
       </c>
       <c r="C16" s="15" t="s">
-        <v>318</v>
+        <v>322</v>
       </c>
       <c r="D16" s="15" t="s">
-        <v>319</v>
+        <v>323</v>
       </c>
       <c r="E16" s="15" t="s">
-        <v>320</v>
+        <v>324</v>
       </c>
       <c r="F16" s="15" t="s">
-        <v>321</v>
+        <v>325</v>
       </c>
       <c r="G16" s="15" t="s">
-        <v>322</v>
+        <v>326</v>
       </c>
       <c r="H16" s="15" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="15" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="B17" s="15" t="s">
-        <v>323</v>
+        <v>327</v>
       </c>
       <c r="C17" s="15" t="s">
-        <v>324</v>
+        <v>328</v>
       </c>
       <c r="D17" s="15" t="s">
-        <v>325</v>
+        <v>329</v>
       </c>
       <c r="E17" s="15" t="s">
-        <v>326</v>
+        <v>330</v>
       </c>
       <c r="F17" s="15" t="s">
-        <v>327</v>
+        <v>331</v>
       </c>
       <c r="G17" s="15" t="s">
-        <v>328</v>
+        <v>332</v>
       </c>
       <c r="H17" s="15" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="15" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="B18" s="15" t="s">
-        <v>329</v>
+        <v>333</v>
       </c>
       <c r="C18" s="15" t="s">
-        <v>330</v>
+        <v>334</v>
       </c>
       <c r="D18" s="15" t="s">
-        <v>331</v>
+        <v>335</v>
       </c>
       <c r="E18" s="15" t="s">
-        <v>332</v>
+        <v>336</v>
       </c>
       <c r="F18" s="15" t="s">
-        <v>333</v>
+        <v>337</v>
       </c>
       <c r="G18" s="15" t="s">
-        <v>334</v>
+        <v>338</v>
       </c>
       <c r="H18" s="15" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="15" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="B19" s="15" t="s">
-        <v>335</v>
+        <v>339</v>
       </c>
       <c r="C19" s="15" t="s">
-        <v>336</v>
+        <v>340</v>
       </c>
       <c r="D19" s="15" t="s">
-        <v>337</v>
+        <v>341</v>
       </c>
       <c r="E19" s="15" t="s">
-        <v>338</v>
+        <v>342</v>
       </c>
       <c r="F19" s="15" t="s">
-        <v>339</v>
+        <v>343</v>
       </c>
       <c r="G19" s="15" t="s">
-        <v>340</v>
+        <v>344</v>
       </c>
       <c r="H19" s="15" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="15" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="B20" s="15" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="C20" s="15" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="D20" s="15" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="E20" s="15" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="F20" s="15" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="G20" s="15" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="H20" s="15" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="15" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="B21" s="15" t="s">
-        <v>341</v>
+        <v>345</v>
       </c>
       <c r="C21" s="15" t="s">
-        <v>342</v>
+        <v>346</v>
       </c>
       <c r="D21" s="15" t="s">
-        <v>343</v>
+        <v>347</v>
       </c>
       <c r="E21" s="15" t="s">
-        <v>344</v>
+        <v>348</v>
       </c>
       <c r="F21" s="15" t="s">
-        <v>345</v>
+        <v>349</v>
       </c>
       <c r="G21" s="15" t="s">
-        <v>346</v>
+        <v>350</v>
       </c>
       <c r="H21" s="15" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="15" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="B22" s="15" t="s">
-        <v>347</v>
+        <v>351</v>
       </c>
       <c r="C22" s="15" t="s">
-        <v>348</v>
+        <v>352</v>
       </c>
       <c r="D22" s="15" t="s">
-        <v>349</v>
+        <v>353</v>
       </c>
       <c r="E22" s="15" t="s">
-        <v>350</v>
+        <v>354</v>
       </c>
       <c r="F22" s="15" t="s">
-        <v>351</v>
+        <v>355</v>
       </c>
       <c r="G22" s="15" t="s">
-        <v>352</v>
+        <v>356</v>
       </c>
       <c r="H22" s="15" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="15" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="B23" s="15" t="s">
-        <v>353</v>
+        <v>357</v>
       </c>
       <c r="C23" s="15" t="s">
-        <v>354</v>
+        <v>358</v>
       </c>
       <c r="D23" s="15" t="s">
-        <v>355</v>
+        <v>359</v>
       </c>
       <c r="E23" s="15" t="s">
-        <v>356</v>
+        <v>360</v>
       </c>
       <c r="F23" s="15" t="s">
-        <v>357</v>
+        <v>361</v>
       </c>
       <c r="G23" s="15" t="s">
-        <v>358</v>
+        <v>362</v>
       </c>
       <c r="H23" s="15" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="15" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="B24" s="15" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="C24" s="15" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="D24" s="15" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="E24" s="15" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="F24" s="15" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="G24" s="15" t="s">
-        <v>359</v>
+        <v>363</v>
       </c>
       <c r="H24" s="15" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="15" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="B25" s="15" t="s">
-        <v>360</v>
+        <v>364</v>
       </c>
       <c r="C25" s="15" t="s">
-        <v>361</v>
+        <v>365</v>
       </c>
       <c r="D25" s="15" t="s">
-        <v>362</v>
+        <v>366</v>
       </c>
       <c r="E25" s="15" t="s">
-        <v>363</v>
+        <v>367</v>
       </c>
       <c r="F25" s="15" t="s">
-        <v>364</v>
+        <v>368</v>
       </c>
       <c r="G25" s="15" t="s">
-        <v>365</v>
+        <v>369</v>
       </c>
       <c r="H25" s="15" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="15" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="B26" s="15" t="s">
-        <v>366</v>
+        <v>370</v>
       </c>
       <c r="C26" s="15" t="s">
-        <v>367</v>
+        <v>371</v>
       </c>
       <c r="D26" s="15" t="s">
-        <v>368</v>
+        <v>372</v>
       </c>
       <c r="E26" s="15" t="s">
-        <v>369</v>
+        <v>373</v>
       </c>
       <c r="F26" s="15" t="s">
-        <v>370</v>
+        <v>374</v>
       </c>
       <c r="G26" s="15" t="s">
-        <v>371</v>
+        <v>375</v>
       </c>
       <c r="H26" s="15" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="15" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="B27" s="15" t="s">
-        <v>372</v>
+        <v>376</v>
       </c>
       <c r="C27" s="15" t="s">
-        <v>373</v>
+        <v>377</v>
       </c>
       <c r="D27" s="15" t="s">
-        <v>374</v>
+        <v>378</v>
       </c>
       <c r="E27" s="15" t="s">
-        <v>375</v>
+        <v>379</v>
       </c>
       <c r="F27" s="15" t="s">
-        <v>376</v>
+        <v>380</v>
       </c>
       <c r="G27" s="15" t="s">
-        <v>377</v>
+        <v>381</v>
       </c>
       <c r="H27" s="15" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="15" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="B28" s="15" t="s">
-        <v>378</v>
+        <v>382</v>
       </c>
       <c r="C28" s="15" t="s">
-        <v>379</v>
+        <v>383</v>
       </c>
       <c r="D28" s="15" t="s">
-        <v>380</v>
+        <v>384</v>
       </c>
       <c r="E28" s="15" t="s">
-        <v>381</v>
+        <v>385</v>
       </c>
       <c r="F28" s="15" t="s">
-        <v>382</v>
+        <v>386</v>
       </c>
       <c r="G28" s="15" t="s">
-        <v>383</v>
+        <v>387</v>
       </c>
       <c r="H28" s="15" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="15" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="B29" s="15" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="C29" s="15" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="D29" s="15" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="E29" s="15" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="F29" s="15" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="G29" s="15" t="s">
-        <v>384</v>
+        <v>388</v>
       </c>
       <c r="H29" s="15" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="15" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="B30" s="15" t="s">
-        <v>385</v>
+        <v>389</v>
       </c>
       <c r="C30" s="15" t="s">
-        <v>386</v>
+        <v>390</v>
       </c>
       <c r="D30" s="15" t="s">
-        <v>387</v>
+        <v>391</v>
       </c>
       <c r="E30" s="15" t="s">
-        <v>388</v>
+        <v>392</v>
       </c>
       <c r="F30" s="15" t="s">
-        <v>389</v>
+        <v>393</v>
       </c>
       <c r="G30" s="15" t="s">
-        <v>390</v>
+        <v>394</v>
       </c>
       <c r="H30" s="15" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="15" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="B31" s="15" t="s">
-        <v>391</v>
+        <v>395</v>
       </c>
       <c r="C31" s="15" t="s">
-        <v>392</v>
+        <v>396</v>
       </c>
       <c r="D31" s="15" t="s">
-        <v>393</v>
+        <v>397</v>
       </c>
       <c r="E31" s="15" t="s">
-        <v>394</v>
+        <v>398</v>
       </c>
       <c r="F31" s="15" t="s">
-        <v>395</v>
+        <v>399</v>
       </c>
       <c r="G31" s="15" t="s">
-        <v>396</v>
+        <v>400</v>
       </c>
       <c r="H31" s="15" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="15" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="B32" s="15" t="s">
-        <v>397</v>
+        <v>401</v>
       </c>
       <c r="C32" s="15" t="s">
-        <v>398</v>
+        <v>402</v>
       </c>
       <c r="D32" s="15" t="s">
-        <v>399</v>
+        <v>403</v>
       </c>
       <c r="E32" s="15" t="s">
-        <v>400</v>
+        <v>404</v>
       </c>
       <c r="F32" s="15" t="s">
-        <v>401</v>
+        <v>405</v>
       </c>
       <c r="G32" s="15" t="s">
-        <v>402</v>
+        <v>406</v>
       </c>
       <c r="H32" s="15" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="15" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="B33" s="15" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="C33" s="15" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="D33" s="15" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="E33" s="15" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="F33" s="15" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="G33" s="15" t="s">
-        <v>403</v>
+        <v>407</v>
       </c>
       <c r="H33" s="15" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="15" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="B34" s="15" t="s">
-        <v>404</v>
+        <v>408</v>
       </c>
       <c r="C34" s="15" t="s">
-        <v>405</v>
+        <v>409</v>
       </c>
       <c r="D34" s="15" t="s">
-        <v>406</v>
+        <v>410</v>
       </c>
       <c r="E34" s="15" t="s">
-        <v>407</v>
+        <v>411</v>
       </c>
       <c r="F34" s="15" t="s">
-        <v>408</v>
+        <v>412</v>
       </c>
       <c r="G34" s="15" t="s">
-        <v>409</v>
+        <v>413</v>
       </c>
       <c r="H34" s="15" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="15" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="B35" s="15" t="s">
-        <v>410</v>
+        <v>414</v>
       </c>
       <c r="C35" s="15" t="s">
-        <v>411</v>
+        <v>415</v>
       </c>
       <c r="D35" s="15" t="s">
-        <v>412</v>
+        <v>416</v>
       </c>
       <c r="E35" s="15" t="s">
-        <v>413</v>
+        <v>417</v>
       </c>
       <c r="F35" s="15" t="s">
-        <v>414</v>
+        <v>418</v>
       </c>
       <c r="G35" s="15" t="s">
-        <v>415</v>
+        <v>419</v>
       </c>
       <c r="H35" s="15" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="15" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="B36" s="15" t="s">
-        <v>416</v>
+        <v>420</v>
       </c>
       <c r="C36" s="15" t="s">
-        <v>417</v>
+        <v>421</v>
       </c>
       <c r="D36" s="15" t="s">
-        <v>418</v>
+        <v>422</v>
       </c>
       <c r="E36" s="15" t="s">
-        <v>419</v>
+        <v>423</v>
       </c>
       <c r="F36" s="15" t="s">
-        <v>420</v>
+        <v>424</v>
       </c>
       <c r="G36" s="15" t="s">
-        <v>421</v>
+        <v>425</v>
       </c>
       <c r="H36" s="15" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="15" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="B37" s="15" t="s">
-        <v>422</v>
+        <v>426</v>
       </c>
       <c r="C37" s="15" t="s">
-        <v>423</v>
+        <v>427</v>
       </c>
       <c r="D37" s="15" t="s">
-        <v>424</v>
+        <v>428</v>
       </c>
       <c r="E37" s="15" t="s">
-        <v>425</v>
+        <v>429</v>
       </c>
       <c r="F37" s="15" t="s">
-        <v>426</v>
+        <v>430</v>
       </c>
       <c r="G37" s="15" t="s">
-        <v>427</v>
+        <v>431</v>
       </c>
       <c r="H37" s="15" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="15" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="B38" s="15" t="s">
-        <v>428</v>
+        <v>432</v>
       </c>
       <c r="C38" s="15" t="s">
-        <v>429</v>
+        <v>433</v>
       </c>
       <c r="D38" s="15" t="s">
-        <v>430</v>
+        <v>434</v>
       </c>
       <c r="E38" s="15" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="F38" s="15" t="s">
-        <v>431</v>
+        <v>435</v>
       </c>
       <c r="G38" s="15" t="s">
-        <v>432</v>
+        <v>436</v>
       </c>
       <c r="H38" s="15" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="15" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="B39" s="15" t="s">
-        <v>433</v>
+        <v>437</v>
       </c>
       <c r="C39" s="15" t="s">
-        <v>434</v>
+        <v>438</v>
       </c>
       <c r="D39" s="15" t="s">
-        <v>435</v>
+        <v>439</v>
       </c>
       <c r="E39" s="15" t="s">
-        <v>436</v>
+        <v>440</v>
       </c>
       <c r="F39" s="15" t="s">
-        <v>437</v>
+        <v>441</v>
       </c>
       <c r="G39" s="15" t="s">
-        <v>438</v>
+        <v>442</v>
       </c>
       <c r="H39" s="15" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="15" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="B40" s="15" t="s">
-        <v>439</v>
+        <v>443</v>
       </c>
       <c r="C40" s="15" t="s">
-        <v>440</v>
+        <v>444</v>
       </c>
       <c r="D40" s="15" t="s">
-        <v>441</v>
+        <v>445</v>
       </c>
       <c r="E40" s="15" t="s">
-        <v>442</v>
+        <v>446</v>
       </c>
       <c r="F40" s="15" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="G40" s="15" t="s">
-        <v>443</v>
+        <v>447</v>
       </c>
       <c r="H40" s="15" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="15" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="B41" s="15" t="s">
-        <v>444</v>
+        <v>448</v>
       </c>
       <c r="C41" s="15" t="s">
-        <v>445</v>
+        <v>449</v>
       </c>
       <c r="D41" s="15" t="s">
-        <v>446</v>
+        <v>450</v>
       </c>
       <c r="E41" s="15" t="s">
-        <v>447</v>
+        <v>451</v>
       </c>
       <c r="F41" s="15" t="s">
-        <v>448</v>
+        <v>452</v>
       </c>
       <c r="G41" s="15" t="s">
-        <v>449</v>
+        <v>453</v>
       </c>
       <c r="H41" s="15" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="15" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="B42" s="15" t="s">
-        <v>450</v>
+        <v>454</v>
       </c>
       <c r="C42" s="15" t="s">
-        <v>451</v>
+        <v>455</v>
       </c>
       <c r="D42" s="15" t="s">
-        <v>452</v>
+        <v>456</v>
       </c>
       <c r="E42" s="15" t="s">
-        <v>453</v>
+        <v>457</v>
       </c>
       <c r="F42" s="15" t="s">
-        <v>454</v>
+        <v>458</v>
       </c>
       <c r="G42" s="15" t="s">
-        <v>455</v>
+        <v>459</v>
       </c>
       <c r="H42" s="15" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="15" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="B43" s="15" t="s">
-        <v>456</v>
+        <v>460</v>
       </c>
       <c r="C43" s="15" t="s">
-        <v>457</v>
+        <v>461</v>
       </c>
       <c r="D43" s="15" t="s">
-        <v>458</v>
+        <v>462</v>
       </c>
       <c r="E43" s="15" t="s">
-        <v>459</v>
+        <v>463</v>
       </c>
       <c r="F43" s="15" t="s">
-        <v>460</v>
+        <v>464</v>
       </c>
       <c r="G43" s="15" t="s">
-        <v>461</v>
+        <v>465</v>
       </c>
       <c r="H43" s="15" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="15" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="B44" s="15" t="s">
-        <v>462</v>
+        <v>466</v>
       </c>
       <c r="C44" s="15" t="s">
-        <v>463</v>
+        <v>467</v>
       </c>
       <c r="D44" s="15" t="s">
-        <v>464</v>
+        <v>468</v>
       </c>
       <c r="E44" s="15" t="s">
-        <v>465</v>
+        <v>469</v>
       </c>
       <c r="F44" s="15" t="s">
-        <v>466</v>
+        <v>470</v>
       </c>
       <c r="G44" s="15" t="s">
-        <v>467</v>
+        <v>471</v>
       </c>
       <c r="H44" s="15" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="15" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="B45" s="15" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="C45" s="15" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="D45" s="15" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="E45" s="15" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="F45" s="15" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="G45" s="15" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="H45" s="15" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="15" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="B46" s="15" t="s">
-        <v>468</v>
+        <v>472</v>
       </c>
       <c r="C46" s="15" t="s">
-        <v>469</v>
+        <v>473</v>
       </c>
       <c r="D46" s="15" t="s">
-        <v>470</v>
+        <v>474</v>
       </c>
       <c r="E46" s="15" t="s">
-        <v>471</v>
+        <v>475</v>
       </c>
       <c r="F46" s="15" t="s">
-        <v>472</v>
+        <v>476</v>
       </c>
       <c r="G46" s="15" t="s">
-        <v>473</v>
+        <v>477</v>
       </c>
       <c r="H46" s="15" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="15" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="B47" s="15" t="s">
-        <v>474</v>
+        <v>478</v>
       </c>
       <c r="C47" s="15" t="s">
-        <v>475</v>
+        <v>479</v>
       </c>
       <c r="D47" s="15" t="s">
-        <v>476</v>
+        <v>480</v>
       </c>
       <c r="E47" s="15" t="s">
-        <v>477</v>
+        <v>481</v>
       </c>
       <c r="F47" s="15" t="s">
-        <v>478</v>
+        <v>482</v>
       </c>
       <c r="G47" s="15" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="H47" s="15" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="15" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="B48" s="15" t="s">
-        <v>479</v>
+        <v>483</v>
       </c>
       <c r="C48" s="15" t="s">
-        <v>480</v>
+        <v>484</v>
       </c>
       <c r="D48" s="15" t="s">
-        <v>481</v>
+        <v>485</v>
       </c>
       <c r="E48" s="15" t="s">
-        <v>482</v>
+        <v>486</v>
       </c>
       <c r="F48" s="15" t="s">
-        <v>482</v>
+        <v>486</v>
       </c>
       <c r="G48" s="15" t="s">
-        <v>483</v>
+        <v>487</v>
       </c>
       <c r="H48" s="15" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="15" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="B49" s="15" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="C49" s="15" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="D49" s="15" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="E49" s="15" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="F49" s="15" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="G49" s="15" t="s">
-        <v>484</v>
+        <v>488</v>
       </c>
       <c r="H49" s="15" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="15" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="B50" s="15" t="s">
-        <v>485</v>
+        <v>489</v>
       </c>
       <c r="C50" s="15" t="s">
-        <v>486</v>
+        <v>490</v>
       </c>
       <c r="D50" s="15" t="s">
-        <v>487</v>
+        <v>491</v>
       </c>
       <c r="E50" s="15" t="s">
-        <v>488</v>
+        <v>492</v>
       </c>
       <c r="F50" s="15" t="s">
-        <v>489</v>
+        <v>493</v>
       </c>
       <c r="G50" s="15" t="s">
-        <v>490</v>
+        <v>494</v>
       </c>
       <c r="H50" s="15" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="15" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="B51" s="15" t="s">
-        <v>491</v>
+        <v>495</v>
       </c>
       <c r="C51" s="15" t="s">
-        <v>492</v>
+        <v>496</v>
       </c>
       <c r="D51" s="15" t="s">
-        <v>493</v>
+        <v>497</v>
       </c>
       <c r="E51" s="15" t="s">
-        <v>494</v>
+        <v>498</v>
       </c>
       <c r="F51" s="15" t="s">
-        <v>495</v>
+        <v>499</v>
       </c>
       <c r="G51" s="15" t="s">
-        <v>496</v>
+        <v>500</v>
       </c>
       <c r="H51" s="15" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
     </row>
   </sheetData>

--- a/output/year1_summary_2026-10-29.xlsx
+++ b/output/year1_summary_2026-10-29.xlsx
@@ -219,7 +219,7 @@
     <t xml:space="preserve">4 Complete of 50</t>
   </si>
   <si>
-    <t xml:space="preserve">States with ≥50% published (n = 22)</t>
+    <t xml:space="preserve">States with ≥50% published, state award sources (n = 21)</t>
   </si>
   <si>
     <t xml:space="preserve">n/m</t>
@@ -516,7 +516,7 @@
     <t xml:space="preserve">US_GE50</t>
   </si>
   <si>
-    <t xml:space="preserve">4 COMPLETE of 22: AK AL AR CA CO FL GA ID IN MD MI MS NJ NV OH OR RI SC SD TX VT WY</t>
+    <t xml:space="preserve">4 COMPLETE of 21: AK AL AR CA CO FL GA ID IN MD MI MS NJ NV OH OR SC SD TX VT WY</t>
   </si>
   <si>
     <t xml:space="preserve">sheet</t>
@@ -531,7 +531,7 @@
     <t xml:space="preserve">Overview</t>
   </si>
   <si>
-    <t xml:space="preserve">State name. Below the 50 states: the national total (the sum of the 50 state rows), then the states whose awards published are at least 50% of their allotment (n in the label), which shows only allotment, awards published, the hospital figures and strict named-hospital dollars. The second row is a subset of the national total, never added to it.</t>
+    <t xml:space="preserve">State name. Below the 50 states: the national total (the sum of the 50 state rows), then the states whose awards published are at least 50% of their allotment and rest on state award sources only (n in the label; a state with any CMS obligation-report row is left out), which shows only allotment, awards published, the hospital figures and strict named-hospital dollars. The second row is a subset of the national total, never added to it.</t>
   </si>
   <si>
     <t xml:space="preserve">Plain-language Year 1 status; each label is defined below.</t>
@@ -582,7 +582,7 @@
     <t xml:space="preserve">Detail</t>
   </si>
   <si>
-    <t xml:space="preserve">Two-letter state code. US is the national row (the sum of the 50 state rows). US_GE50 is the second national row: the sum over the states whose awards published are at least 50% of their allotment (a subset of US, never added to it).</t>
+    <t xml:space="preserve">Two-letter state code. US is the national row (the sum of the 50 state rows). US_GE50 is the second national row: the sum over the states whose awards published are at least 50% of their allotment AND rest on state award sources only (a state with any CMS obligation-report row, such as Rhode Island, is left out); a subset of US, never added to it.</t>
   </si>
   <si>
     <t xml:space="preserve">State name.</t>
@@ -735,7 +735,7 @@
     <t xml:space="preserve">n/m (HOSPITAL % OF AWARDS). Shown only where awards published are at least 50% of the allotment. Not meaningful where most of the state's money is not yet published; e.g., Illinois's only published award is ICAHN's hospital network grant. The national hospital share of awards is reported only for states where most of the money is published (see the second national row). Hospital % of allotment is shown for every state.</t>
   </si>
   <si>
-    <t xml:space="preserve">SECOND NATIONAL ROW. 'States with ≥50% published (n = 22)' sums the states whose awards published are at least 50% of their allotment (AK AL AR CA CO FL GA ID IN MD MI MS NJ NV OH OR RI SC SD TX VT WY): allotment $4,440,562,268, awards published $3,441,569,061, hospital best estimate $1,572,986,177 (45.7% of those awards). It is a subset of the national row, never added to it. Rhode Island qualifies on CMS obligation-report lines alone; the set changes as states publish.</t>
+    <t xml:space="preserve">SECOND NATIONAL ROW. 'States with ≥50% published, state award sources (n = 21)' sums the states whose awards published are at least 50% of their allotment AND rest on state award sources only: a state with any award row taken from CMS's Obligated Funds Report is left out, whatever its share (excluded today: Rhode Island (50.4%, CMS obligation lines)). Members (AK AL AR CA CO FL GA ID IN MD MI MS NJ NV OH OR SC SD TX VT WY): allotment $4,284,392,337, awards published $3,362,841,951, hospital best estimate $1,557,146,270 (46.3% of those awards). It is a subset of the national row, never added to it; the set changes as states publish.</t>
   </si>
   <si>
     <t xml:space="preserve">CONFIDENTIAL SOURCES. Figures or rows flagged here rest on, or cite, Delaware's confidential source (DE Verify.xlsx). They must not leave the team. As built, no award row or figure cites it; Delaware's status-table notes do (confidential_source_flag; the row is shaded on Overview and Detail).</t>
@@ -1900,7 +1900,7 @@
   <dimension ref="A1"/>
   <sheetFormatPr defaultRowHeight="15.0" baseColWidth="10"/>
   <cols>
-    <col min="1" max="1" width="38.71" hidden="0" customWidth="1"/>
+    <col min="1" max="1" width="59.71" hidden="0" customWidth="1"/>
     <col min="2" max="2" width="31.71" hidden="0" customWidth="1"/>
     <col min="3" max="3" width="19.71" hidden="0" customWidth="1"/>
     <col min="4" max="4" width="19.71" hidden="0" customWidth="1"/>
@@ -3582,20 +3582,20 @@
       </c>
       <c r="B53" s="8"/>
       <c r="C53" s="5" t="n">
-        <v>4440562268</v>
+        <v>4284392337</v>
       </c>
       <c r="D53" s="5" t="n">
-        <v>3441569061.22</v>
+        <v>3362841950.78</v>
       </c>
       <c r="E53" s="6"/>
       <c r="F53" s="5" t="n">
-        <v>1572986177.36</v>
+        <v>1557146269.69</v>
       </c>
       <c r="G53" s="6" t="n">
-        <v>0.45705495062836</v>
+        <v>0.463044737897606</v>
       </c>
       <c r="H53" s="6" t="n">
-        <v>0.354231307304348</v>
+        <v>0.363446236294116</v>
       </c>
       <c r="I53" s="5" t="n">
         <v>1451104633.38</v>
@@ -3614,7 +3614,7 @@
   <sheetFormatPr defaultRowHeight="15.0" baseColWidth="10"/>
   <cols>
     <col min="1" max="1" width="10.71" hidden="0" customWidth="1"/>
-    <col min="2" max="2" width="38.71" hidden="0" customWidth="1"/>
+    <col min="2" max="2" width="59.71" hidden="0" customWidth="1"/>
     <col min="3" max="3" width="60.71" hidden="0" customWidth="1"/>
     <col min="4" max="4" width="18.71" hidden="0" customWidth="1"/>
     <col min="5" max="5" width="14.71" hidden="0" customWidth="1"/>
@@ -9539,37 +9539,37 @@
         <v>166</v>
       </c>
       <c r="D53" s="5" t="n">
-        <v>4440562268</v>
+        <v>4284392337</v>
       </c>
       <c r="E53" s="8" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="F53" s="8" t="n">
-        <v>3441</v>
+        <v>3337</v>
       </c>
       <c r="G53" s="8" t="n">
-        <v>3125</v>
+        <v>3021</v>
       </c>
       <c r="H53" s="5" t="n">
-        <v>3028965541.22</v>
+        <v>2950238430.78</v>
       </c>
       <c r="I53" s="5" t="n">
         <v>412603520</v>
       </c>
       <c r="J53" s="5" t="n">
-        <v>3441569061.22</v>
+        <v>3362841950.78</v>
       </c>
       <c r="K53" s="6" t="n">
-        <v>0.775030019513736</v>
+        <v>0.784905229555778</v>
       </c>
       <c r="L53" s="5" t="n">
         <v>1385478477.61</v>
       </c>
       <c r="M53" s="8" t="n">
-        <v>1355</v>
+        <v>1353</v>
       </c>
       <c r="N53" s="5" t="n">
-        <v>1446728679.7</v>
+        <v>1430888772.03</v>
       </c>
       <c r="O53" s="5" t="n">
         <v>126257497.66</v>
@@ -9584,16 +9584,16 @@
         <v>0</v>
       </c>
       <c r="S53" s="8" t="n">
-        <v>438</v>
+        <v>433</v>
       </c>
       <c r="T53" s="5" t="n">
-        <v>1572986177.36</v>
+        <v>1557146269.69</v>
       </c>
       <c r="U53" s="6" t="n">
-        <v>0.45705495062836</v>
+        <v>0.463044737897606</v>
       </c>
       <c r="V53" s="6" t="n">
-        <v>0.354231307304348</v>
+        <v>0.363446236294116</v>
       </c>
       <c r="W53" s="5" t="n">
         <v>1451104633.38</v>
@@ -9602,25 +9602,25 @@
         <v>54748315.31</v>
       </c>
       <c r="Y53" s="5" t="n">
-        <v>15839907.67</v>
+        <v>0</v>
       </c>
       <c r="Z53" s="5" t="n">
         <v>710051173.87</v>
       </c>
       <c r="AA53" s="5" t="n">
-        <v>52746543.98</v>
+        <v>36906636.31</v>
       </c>
       <c r="AB53" s="5" t="n">
-        <v>15839907.67</v>
+        <v>0</v>
       </c>
       <c r="AC53" s="5" t="n">
         <v>55305273.31</v>
       </c>
       <c r="AD53" s="5" t="n">
-        <v>126762455.53</v>
+        <v>110922547.86</v>
       </c>
       <c r="AE53" s="5" t="n">
-        <v>253328337.11</v>
+        <v>237488429.44</v>
       </c>
       <c r="AF53" s="5" t="n">
         <v>512424850.1</v>

--- a/output/year1_summary_2026-10-29.xlsx
+++ b/output/year1_summary_2026-10-29.xlsx
@@ -531,7 +531,7 @@
     <t xml:space="preserve">Overview</t>
   </si>
   <si>
-    <t xml:space="preserve">State name. Below the 50 states: the national total (the sum of the 50 state rows), then the states whose awards published are at least 50% of their allotment and rest on state award sources only (n in the label; a state with any CMS obligation-report row is left out), which shows only allotment, awards published, the hospital figures and strict named-hospital dollars. The second row is a subset of the national total, never added to it.</t>
+    <t xml:space="preserve">State name. Below the 50 states: the national total (the sum of the 50 state rows), then the states whose state-sourced awards published are at least 50% of their allotment (n in the label; CMS obligation-report rows are removed from that row's figures and from each state's test), which shows only allotment, awards published, the hospital figures and strict named-hospital dollars. The second row is a subset of the national total, never added to it.</t>
   </si>
   <si>
     <t xml:space="preserve">Plain-language Year 1 status; each label is defined below.</t>
@@ -582,7 +582,7 @@
     <t xml:space="preserve">Detail</t>
   </si>
   <si>
-    <t xml:space="preserve">Two-letter state code. US is the national row (the sum of the 50 state rows). US_GE50 is the second national row: the sum over the states whose awards published are at least 50% of their allotment AND rest on state award sources only (a state with any CMS obligation-report row, such as Rhode Island, is left out); a subset of US, never added to it.</t>
+    <t xml:space="preserve">Two-letter state code. US is the national row (the sum of the 50 state rows). US_GE50 is the second national row, on state award sources only: CMS obligation-report rows are removed from all its figures, and it sums the states whose state-sourced awards published are at least 50% of their allotment (Rhode Island, whose only rows are CMS lines, cannot qualify); a subset of US, never added to it.</t>
   </si>
   <si>
     <t xml:space="preserve">State name.</t>
@@ -735,7 +735,7 @@
     <t xml:space="preserve">n/m (HOSPITAL % OF AWARDS). Shown only where awards published are at least 50% of the allotment. Not meaningful where most of the state's money is not yet published; e.g., Illinois's only published award is ICAHN's hospital network grant. The national hospital share of awards is reported only for states where most of the money is published (see the second national row). Hospital % of allotment is shown for every state.</t>
   </si>
   <si>
-    <t xml:space="preserve">SECOND NATIONAL ROW. 'States with ≥50% published, state award sources (n = 21)' sums the states whose awards published are at least 50% of their allotment AND rest on state award sources only: a state with any award row taken from CMS's Obligated Funds Report is left out, whatever its share (excluded today: Rhode Island (50.4%, CMS obligation lines)). Members (AK AL AR CA CO FL GA ID IN MD MI MS NJ NV OH OR SC SD TX VT WY): allotment $4,284,392,337, awards published $3,362,841,951, hospital best estimate $1,557,146,270 (46.3% of those awards). It is a subset of the national row, never added to it; the set changes as states publish.</t>
+    <t xml:space="preserve">SECOND NATIONAL ROW. 'States with ≥50% published, state award sources (n = 21)' rests on state award sources only. Rows taken from CMS's Obligated Funds Report are removed from every figure in it, each state's '% published' is computed on its state-sourced awards alone, and a state qualifies when those are at least 50% of its allotment. States carrying CMS obligation lines today: Nebraska 19.1% state-sourced (20.9% with CMS lines; does not qualify); Pennsylvania 21.8% state-sourced (23.4% with CMS lines; does not qualify); Rhode Island 0.0% state-sourced (50.4% with CMS lines; does not qualify). Members (AK AL AR CA CO FL GA ID IN MD MI MS NJ NV OH OR SC SD TX VT WY): allotment $4,284,392,337, awards published $3,362,841,951, hospital best estimate $1,557,146,270 (46.3% of those awards). It is a subset of the national row, never added to it; the set changes as states publish.</t>
   </si>
   <si>
     <t xml:space="preserve">CONFIDENTIAL SOURCES. Figures or rows flagged here rest on, or cite, Delaware's confidential source (DE Verify.xlsx). They must not leave the team. As built, no award row or figure cites it; Delaware's status-table notes do (confidential_source_flag; the row is shaded on Overview and Detail).</t>

--- a/output/year1_summary_2026-10-29.xlsx
+++ b/output/year1_summary_2026-10-29.xlsx
@@ -549,7 +549,7 @@
     <t xml:space="preserve">BEST ESTIMATE of Year 1 RHTP dollars reaching hospitals: source-coded plus best-judgment hospital dollars (Detail: hospital_summary_usd).</t>
   </si>
   <si>
-    <t xml:space="preserve">Best-estimate hospital dollars as a share of awards published. Shown only where awards published are at least 50% of the allotment; otherwise n/m (not meaningful) (Detail: hospital_share_of_awards_pct).</t>
+    <t xml:space="preserve">Best-estimate hospital dollars as a share of awards published. Shown only where the state's STATE-SOURCED awards published (CMS obligation-report rows left out) are at least 50% of its allotment; otherwise n/m (not meaningful) (Detail: hospital_share_of_awards_pct).</t>
   </si>
   <si>
     <t xml:space="preserve">Best-estimate hospital dollars as a share of the allotment, shown for every state (Detail: hospital_share_of_allotment_pct).</t>
@@ -642,7 +642,7 @@
     <t xml:space="preserve">BEST ESTIMATE of Year 1 RHTP dollars reaching hospitals: coded plus best-judgment hospital dollars.</t>
   </si>
   <si>
-    <t xml:space="preserve">Best-estimate hospital dollars as a percent of the published award total.</t>
+    <t xml:space="preserve">Best-estimate hospital dollars as a percent of the published award total. On the workbook's Detail sheet it reads n/m where the state's state-sourced awards (CMS obligation-report rows left out) are under 50% of its allotment; this CSV keeps the computed value.</t>
   </si>
   <si>
     <t xml:space="preserve">Best-estimate hospital dollars as a percent of the allotment.</t>
@@ -732,7 +732,7 @@
     <t xml:space="preserve">AWARD COVERAGE VARIES WIDELY BY STATE. Awards published run from 0% to 97.6% of the allotment, so a state's hospital share describes only the money that state has published so far. State shares are not comparable to one another.</t>
   </si>
   <si>
-    <t xml:space="preserve">n/m (HOSPITAL % OF AWARDS). Shown only where awards published are at least 50% of the allotment. Not meaningful where most of the state's money is not yet published; e.g., Illinois's only published award is ICAHN's hospital network grant. The national hospital share of awards is reported only for states where most of the money is published (see the second national row). Hospital % of allotment is shown for every state.</t>
+    <t xml:space="preserve">n/m (HOSPITAL % OF AWARDS). Shown only where the state's STATE-SOURCED awards published are at least 50% of its allotment: rows taken from CMS's Obligated Funds Report do not count toward the test, the same rule as the second national row (Rhode Island, whose only rows are CMS lines, reads n/m). Not meaningful where most of the state's money is not yet published; e.g., Illinois's only published award is ICAHN's hospital network grant. The national hospital share of awards is reported only for states where most of the money is published (see the second national row). Hospital % of allotment is shown for every state.</t>
   </si>
   <si>
     <t xml:space="preserve">SECOND NATIONAL ROW. 'States with ≥50% published, state award sources (n = 21)' rests on state award sources only. Rows taken from CMS's Obligated Funds Report are removed from every figure in it, each state's '% published' is computed on its state-sourced awards alone, and a state qualifies when those are at least 50% of its allotment. States carrying CMS obligation lines today: Nebraska 19.1% state-sourced (20.9% with CMS lines; does not qualify); Pennsylvania 21.8% state-sourced (23.4% with CMS lines; does not qualify); Rhode Island 0.0% state-sourced (50.4% with CMS lines; does not qualify). Members (AK AL AR CA CO FL GA ID IN MD MI MS NJ NV OH OR SC SD TX VT WY): allotment $4,284,392,337, awards published $3,362,841,951, hospital best estimate $1,557,146,270 (46.3% of those awards). It is a subset of the national row, never added to it; the set changes as states publish.</t>
@@ -3179,8 +3179,8 @@
       <c r="F40" s="2" t="n">
         <v>15839907.67</v>
       </c>
-      <c r="G40" s="3" t="n">
-        <v>0.20120016575576</v>
+      <c r="G40" s="4" t="s">
+        <v>68</v>
       </c>
       <c r="H40" s="3" t="n">
         <v>0.101427384699299</v>
@@ -8120,8 +8120,8 @@
       <c r="T40" s="2" t="n">
         <v>15839907.67</v>
       </c>
-      <c r="U40" s="3" t="n">
-        <v>0.20120016575576</v>
+      <c r="U40" s="4" t="s">
+        <v>68</v>
       </c>
       <c r="V40" s="3" t="n">
         <v>0.101427384699299</v>
